--- a/grupos/2AEV - Estadisticos 20222.xlsx
+++ b/grupos/2AEV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -195,12 +195,12 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
@@ -246,220 +246,220 @@
     <t>LOBATO</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>PUGA CABRERA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>TZOMPOLE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>CAZARES</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>JOSE RAMON</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>GERSON</t>
+  </si>
+  <si>
+    <t>LEONEL FELIPE</t>
+  </si>
+  <si>
+    <t>LUIS DAVID</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>HECTOR ALAN</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>JESUS IVAN</t>
+  </si>
+  <si>
+    <t>ELIAS</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
+    <t>ABDIEL NOE</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>JOSE LEONARDO</t>
+  </si>
+  <si>
+    <t>NAHUM HIRAM</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>CAZARES</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>JOSE RAMON</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>GERSON</t>
-  </si>
-  <si>
-    <t>LEONEL FELIPE</t>
-  </si>
-  <si>
-    <t>LUIS DAVID</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>HECTOR ALAN</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>PAUL ARAVIER</t>
   </si>
   <si>
     <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>JESUS IVAN</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
   </si>
   <si>
     <t>DIEGO IVAN</t>
@@ -951,7 +951,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>-1</v>
@@ -1005,7 +1005,7 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -1057,7 +1057,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>-1</v>
@@ -1111,7 +1111,7 @@
         <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1134,7 +1134,7 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>-1</v>
@@ -1188,7 +1188,7 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1211,7 +1211,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>-1</v>
@@ -1265,7 +1265,7 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1288,13 +1288,13 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>-1</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -1342,13 +1342,13 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1365,7 +1365,7 @@
         <v>4</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>-1</v>
@@ -1419,7 +1419,7 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1442,7 +1442,7 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>-1</v>
@@ -1496,7 +1496,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1519,7 +1519,7 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>-1</v>
@@ -1573,7 +1573,7 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1596,7 +1596,7 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>-1</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1673,7 +1673,7 @@
         <v>8</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>-1</v>
@@ -1727,7 +1727,7 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1750,7 +1750,7 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>-1</v>
@@ -1804,7 +1804,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1827,13 +1827,13 @@
         <v>5</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>-1</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>6</v>
@@ -1881,13 +1881,13 @@
         <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1904,13 +1904,13 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>-1</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -1958,13 +1958,13 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -1981,10 +1981,10 @@
         <v>4</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -2026,10 +2026,10 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -2046,7 +2046,7 @@
         <v>4</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>-1</v>
@@ -2100,7 +2100,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2123,13 +2123,13 @@
         <v>4</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>-1</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -2177,13 +2177,13 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2200,7 +2200,7 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>-1</v>
@@ -2254,7 +2254,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2277,7 +2277,7 @@
         <v>9</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>-1</v>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2354,7 +2354,7 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>-1</v>
@@ -2408,7 +2408,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2460,13 +2460,13 @@
         <v>4</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>-1</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -2514,13 +2514,13 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -2537,7 +2537,7 @@
         <v>9</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>-1</v>
@@ -2591,7 +2591,7 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2614,7 +2614,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>-1</v>
@@ -2668,7 +2668,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>-1</v>
@@ -2691,7 +2691,7 @@
         <v>4</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>-1</v>
@@ -2745,7 +2745,7 @@
         <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -2768,13 +2768,13 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>-1</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -2822,13 +2822,13 @@
         <v>5</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -2845,7 +2845,7 @@
         <v>8</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>-1</v>
@@ -2899,7 +2899,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>-1</v>
@@ -2922,7 +2922,7 @@
         <v>4</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D31">
         <v>-1</v>
@@ -2976,7 +2976,7 @@
         <v>5</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -2999,7 +2999,7 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>-1</v>
@@ -3053,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3076,7 +3076,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>-1</v>
@@ -3130,7 +3130,7 @@
         <v>6</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>-1</v>
@@ -3153,7 +3153,7 @@
         <v>4</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>-1</v>
@@ -3207,7 +3207,7 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>-1</v>
@@ -3230,7 +3230,7 @@
         <v>7</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>-1</v>
@@ -3284,7 +3284,7 @@
         <v>7</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>-1</v>
@@ -3307,7 +3307,7 @@
         <v>4</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>-1</v>
@@ -3361,7 +3361,7 @@
         <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>-1</v>
@@ -3494,7 +3494,7 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -3576,7 +3576,7 @@
         <v>93.3</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -3635,7 +3635,7 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>80</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -3753,13 +3753,13 @@
         <v>80</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F9">
         <v>80</v>
@@ -3812,7 +3812,7 @@
         <v>33.3</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -3930,7 +3930,7 @@
         <v>93.3</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -3989,7 +3989,7 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -4048,7 +4048,7 @@
         <v>93.3</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -4107,7 +4107,7 @@
         <v>93.3</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -4166,13 +4166,13 @@
         <v>93.3</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -4225,13 +4225,13 @@
         <v>80</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F17">
         <v>85</v>
@@ -4284,10 +4284,10 @@
         <v>76.7</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F18">
         <v>85</v>
@@ -4334,7 +4334,7 @@
         <v>76.7</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -4393,13 +4393,13 @@
         <v>20</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F20">
         <v>80</v>
@@ -4452,7 +4452,7 @@
         <v>93.3</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -4511,7 +4511,7 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -4570,7 +4570,7 @@
         <v>96.7</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -4652,13 +4652,13 @@
         <v>73.3</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="F25">
         <v>95</v>
@@ -4711,7 +4711,7 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -4770,7 +4770,7 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -4829,7 +4829,7 @@
         <v>66.7</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -4888,13 +4888,13 @@
         <v>80</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F29">
         <v>95</v>
@@ -4947,7 +4947,7 @@
         <v>93.3</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -5006,7 +5006,7 @@
         <v>73.3</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -5065,7 +5065,7 @@
         <v>93.3</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -5124,7 +5124,7 @@
         <v>80</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>80</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -5242,7 +5242,7 @@
         <v>93.3</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -5301,7 +5301,7 @@
         <v>80</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -5433,57 +5433,60 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>45.45</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>54.55</v>
+      </c>
+      <c r="H3">
+        <v>6.1</v>
       </c>
       <c r="I3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>15</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>45.45</v>
+        <v>48.39</v>
       </c>
       <c r="G4">
-        <v>54.55</v>
+        <v>51.61</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5497,7 +5500,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>33</v>
@@ -5570,22 +5573,22 @@
         <v>22</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F7">
         <v>70.97</v>
       </c>
       <c r="G7">
-        <v>6.45</v>
+        <v>29.03</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>22.58</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5595,7 +5598,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5630,10 +5633,10 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5644,36 +5647,36 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920177</v>
+        <v>22330051920178</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
         <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920178</v>
+        <v>22330051920179</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
         <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5684,33 +5687,33 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920178</v>
+        <v>22330051920181</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
         <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920179</v>
+        <v>22330051920389</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
         <v>113</v>
@@ -5724,56 +5727,56 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920179</v>
+        <v>22330051920183</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920181</v>
+        <v>22330051920184</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920181</v>
+        <v>22330051920185</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5784,36 +5787,36 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920181</v>
+        <v>22330051920188</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920389</v>
+        <v>22330051920187</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -5824,36 +5827,36 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920389</v>
+        <v>22330051920190</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920183</v>
+        <v>22330051920413</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -5864,36 +5867,36 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920183</v>
+        <v>22330051920388</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920184</v>
+        <v>22330051920378</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -5904,36 +5907,36 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920184</v>
+        <v>22330051920359</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920185</v>
+        <v>22330051920192</v>
       </c>
       <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
         <v>72</v>
       </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -5944,36 +5947,36 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920185</v>
+        <v>22330051920193</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920188</v>
+        <v>22330051920195</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -5984,36 +5987,33 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920188</v>
+        <v>22330051920197</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920187</v>
+        <v>22330051920358</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -6024,56 +6024,56 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920187</v>
+        <v>22330051920356</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920190</v>
+        <v>22330051920180</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920190</v>
+        <v>22330051920363</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -6084,56 +6084,56 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920190</v>
+        <v>22330051920390</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>22330051920413</v>
+        <v>22330051920199</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920413</v>
+        <v>22330051920200</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -6144,836 +6144,82 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>22330051920413</v>
+        <v>22330051920371</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920014</v>
+        <v>22330051920201</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920014</v>
+        <v>22330051920202</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>22330051920388</v>
+        <v>22330051920204</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920388</v>
-      </c>
-      <c r="B32" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" t="s">
-        <v>124</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920388</v>
-      </c>
-      <c r="B33" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" t="s">
-        <v>124</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920378</v>
-      </c>
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" t="s">
-        <v>125</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920378</v>
-      </c>
-      <c r="B35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" t="s">
-        <v>125</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920359</v>
-      </c>
-      <c r="B36" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920359</v>
-      </c>
-      <c r="B37" t="s">
-        <v>77</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>126</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920192</v>
-      </c>
-      <c r="B38" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" t="s">
-        <v>72</v>
-      </c>
-      <c r="D38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920192</v>
-      </c>
-      <c r="B39" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D39" t="s">
-        <v>127</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920193</v>
-      </c>
-      <c r="B40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" t="s">
-        <v>128</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920193</v>
-      </c>
-      <c r="B41" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" t="s">
-        <v>104</v>
-      </c>
-      <c r="D41" t="s">
-        <v>128</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>22330051920195</v>
-      </c>
-      <c r="B42" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" t="s">
-        <v>105</v>
-      </c>
-      <c r="D42" t="s">
-        <v>129</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>22330051920195</v>
-      </c>
-      <c r="B43" t="s">
-        <v>80</v>
-      </c>
-      <c r="C43" t="s">
-        <v>105</v>
-      </c>
-      <c r="D43" t="s">
-        <v>129</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>22330051920195</v>
-      </c>
-      <c r="B44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" t="s">
-        <v>129</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>22330051920197</v>
-      </c>
-      <c r="B45" t="s">
-        <v>81</v>
-      </c>
-      <c r="D45" t="s">
-        <v>130</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>22330051920197</v>
-      </c>
-      <c r="B46" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" t="s">
-        <v>130</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>22330051920358</v>
-      </c>
-      <c r="B47" t="s">
-        <v>82</v>
-      </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" t="s">
-        <v>131</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>22330051920358</v>
-      </c>
-      <c r="B48" t="s">
-        <v>82</v>
-      </c>
-      <c r="C48" t="s">
-        <v>106</v>
-      </c>
-      <c r="D48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>22330051920356</v>
-      </c>
-      <c r="B49" t="s">
-        <v>83</v>
-      </c>
-      <c r="C49" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" t="s">
-        <v>132</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>22330051920356</v>
-      </c>
-      <c r="B50" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" t="s">
-        <v>132</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>22330051920180</v>
-      </c>
-      <c r="B51" t="s">
-        <v>84</v>
-      </c>
-      <c r="C51" t="s">
-        <v>72</v>
-      </c>
-      <c r="D51" t="s">
-        <v>133</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>22330051920180</v>
-      </c>
-      <c r="B52" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" t="s">
-        <v>72</v>
-      </c>
-      <c r="D52" t="s">
-        <v>133</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>22330051920363</v>
-      </c>
-      <c r="B53" t="s">
-        <v>85</v>
-      </c>
-      <c r="C53" t="s">
-        <v>90</v>
-      </c>
-      <c r="D53" t="s">
-        <v>134</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>22330051920363</v>
-      </c>
-      <c r="B54" t="s">
-        <v>85</v>
-      </c>
-      <c r="C54" t="s">
-        <v>90</v>
-      </c>
-      <c r="D54" t="s">
-        <v>134</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>22330051920390</v>
-      </c>
-      <c r="B55" t="s">
-        <v>86</v>
-      </c>
-      <c r="C55" t="s">
-        <v>108</v>
-      </c>
-      <c r="D55" t="s">
-        <v>135</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>22330051920390</v>
-      </c>
-      <c r="B56" t="s">
-        <v>86</v>
-      </c>
-      <c r="C56" t="s">
-        <v>108</v>
-      </c>
-      <c r="D56" t="s">
-        <v>135</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>22330051920390</v>
-      </c>
-      <c r="B57" t="s">
-        <v>86</v>
-      </c>
-      <c r="C57" t="s">
-        <v>108</v>
-      </c>
-      <c r="D57" t="s">
-        <v>135</v>
-      </c>
-      <c r="E57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>22330051920199</v>
-      </c>
-      <c r="B58" t="s">
-        <v>87</v>
-      </c>
-      <c r="C58" t="s">
-        <v>109</v>
-      </c>
-      <c r="D58" t="s">
-        <v>136</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>22330051920199</v>
-      </c>
-      <c r="B59" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" t="s">
-        <v>109</v>
-      </c>
-      <c r="D59" t="s">
-        <v>136</v>
-      </c>
-      <c r="E59" t="s">
-        <v>6</v>
-      </c>
-      <c r="F59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>22330051920200</v>
-      </c>
-      <c r="B60" t="s">
-        <v>88</v>
-      </c>
-      <c r="C60" t="s">
-        <v>109</v>
-      </c>
-      <c r="D60" t="s">
-        <v>137</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>22330051920200</v>
-      </c>
-      <c r="B61" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61" t="s">
-        <v>109</v>
-      </c>
-      <c r="D61" t="s">
-        <v>137</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>22330051920371</v>
-      </c>
-      <c r="B62" t="s">
-        <v>89</v>
-      </c>
-      <c r="C62" t="s">
-        <v>71</v>
-      </c>
-      <c r="D62" t="s">
-        <v>138</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>22330051920371</v>
-      </c>
-      <c r="B63" t="s">
-        <v>89</v>
-      </c>
-      <c r="C63" t="s">
-        <v>71</v>
-      </c>
-      <c r="D63" t="s">
-        <v>138</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>22330051920201</v>
-      </c>
-      <c r="B64" t="s">
-        <v>90</v>
-      </c>
-      <c r="C64" t="s">
-        <v>109</v>
-      </c>
-      <c r="D64" t="s">
-        <v>139</v>
-      </c>
-      <c r="E64" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>22330051920201</v>
-      </c>
-      <c r="B65" t="s">
-        <v>90</v>
-      </c>
-      <c r="C65" t="s">
-        <v>109</v>
-      </c>
-      <c r="D65" t="s">
-        <v>139</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>22330051920202</v>
-      </c>
-      <c r="B66" t="s">
-        <v>90</v>
-      </c>
-      <c r="C66" t="s">
-        <v>109</v>
-      </c>
-      <c r="D66" t="s">
-        <v>140</v>
-      </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>22330051920202</v>
-      </c>
-      <c r="B67" t="s">
-        <v>90</v>
-      </c>
-      <c r="C67" t="s">
-        <v>109</v>
-      </c>
-      <c r="D67" t="s">
-        <v>140</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>22330051920204</v>
-      </c>
-      <c r="B68" t="s">
-        <v>91</v>
-      </c>
-      <c r="C68" t="s">
-        <v>110</v>
-      </c>
-      <c r="D68" t="s">
-        <v>141</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>22330051920204</v>
-      </c>
-      <c r="B69" t="s">
-        <v>91</v>
-      </c>
-      <c r="C69" t="s">
-        <v>110</v>
-      </c>
-      <c r="D69" t="s">
-        <v>141</v>
-      </c>
-      <c r="E69" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -7009,282 +6255,282 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920181</v>
+        <v>22330051920177</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920190</v>
+        <v>22330051920178</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920413</v>
+        <v>22330051920179</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920388</v>
+        <v>22330051920181</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920195</v>
+        <v>22330051920389</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920390</v>
+        <v>22330051920183</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920177</v>
+        <v>22330051920184</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920178</v>
+        <v>22330051920185</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920179</v>
+        <v>22330051920188</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920389</v>
+        <v>22330051920187</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920183</v>
+        <v>22330051920190</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920184</v>
+        <v>22330051920413</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920185</v>
+        <v>22330051920388</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920188</v>
+        <v>22330051920378</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920187</v>
+        <v>22330051920359</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920014</v>
+        <v>22330051920192</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920378</v>
+        <v>22330051920193</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
         <v>102</v>
@@ -7293,15 +6539,15 @@
         <v>125</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920359</v>
+        <v>22330051920195</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
         <v>103</v>
@@ -7310,32 +6556,29 @@
         <v>126</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920192</v>
+        <v>22330051920197</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
         <v>127</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920193</v>
+        <v>22330051920358</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
         <v>104</v>
@@ -7344,202 +6587,205 @@
         <v>128</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920197</v>
+        <v>22330051920356</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920358</v>
+        <v>22330051920180</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920356</v>
+        <v>22330051920363</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920180</v>
+        <v>22330051920390</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920363</v>
+        <v>22330051920199</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920199</v>
+        <v>22330051920200</v>
       </c>
       <c r="B27" t="s">
         <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920200</v>
+        <v>22330051920371</v>
       </c>
       <c r="B28" t="s">
         <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920371</v>
+        <v>22330051920201</v>
       </c>
       <c r="B29" t="s">
         <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920201</v>
+        <v>22330051920202</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920202</v>
+        <v>22330051920204</v>
       </c>
       <c r="B31" t="s">
         <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920204</v>
+        <v>20330051920072</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920072</v>
+        <v>21330051920014</v>
       </c>
       <c r="B33" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -7553,10 +6799,10 @@
         <v>20330051920090</v>
       </c>
       <c r="B34" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D34" t="s">
         <v>147</v>
@@ -7572,7 +6818,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7604,22 +6850,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920177</v>
+        <v>22330051920184</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -7627,62 +6873,62 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920177</v>
+        <v>22330051920184</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920179</v>
+        <v>22330051920378</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920179</v>
+        <v>22330051920378</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -7696,39 +6942,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920183</v>
+        <v>22330051920200</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920183</v>
+        <v>22330051920200</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -7742,39 +6988,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920185</v>
+        <v>22330051920371</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920185</v>
+        <v>22330051920371</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -7788,22 +7034,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920188</v>
+        <v>22330051920202</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -7811,45 +7057,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920188</v>
+        <v>22330051920202</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920187</v>
+        <v>22330051920177</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -7857,45 +7103,45 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920187</v>
+        <v>20330051920072</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920378</v>
+        <v>22330051920179</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -7903,16 +7149,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920378</v>
+        <v>22330051920183</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -7926,22 +7172,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920192</v>
+        <v>22330051920185</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -7949,16 +7195,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920192</v>
+        <v>22330051920188</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -7972,19 +7218,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920197</v>
+        <v>22330051920187</v>
       </c>
       <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
         <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -7992,13 +7241,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920197</v>
+        <v>22330051920192</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -8012,39 +7264,36 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920358</v>
+        <v>20330051920090</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920358</v>
+        <v>22330051920197</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -8058,22 +7307,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920363</v>
+        <v>22330051920358</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G22">
         <v>-1</v>
@@ -8084,13 +7333,13 @@
         <v>22330051920363</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -8100,144 +7349,6 @@
       </c>
       <c r="G23">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920200</v>
-      </c>
-      <c r="B24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920200</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920371</v>
-      </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920371</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>71</v>
-      </c>
-      <c r="D27" t="s">
-        <v>138</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920072</v>
-      </c>
-      <c r="B28" t="s">
-        <v>142</v>
-      </c>
-      <c r="C28" t="s">
-        <v>144</v>
-      </c>
-      <c r="D28" t="s">
-        <v>146</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920090</v>
-      </c>
-      <c r="B29" t="s">
-        <v>143</v>
-      </c>
-      <c r="C29" t="s">
-        <v>145</v>
-      </c>
-      <c r="D29" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>58</v>
-      </c>
-      <c r="G29">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2AEV - Estadisticos 20222.xlsx
+++ b/grupos/2AEV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -222,6 +222,9 @@
     <t>CAMPOS</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>CHICO</t>
   </si>
   <si>
@@ -246,6 +249,9 @@
     <t>LOBATO</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -255,6 +261,9 @@
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
@@ -297,6 +306,9 @@
     <t>CABRERA</t>
   </si>
   <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -318,6 +330,9 @@
     <t>CIRUELO</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
@@ -327,6 +342,9 @@
     <t>TIZA</t>
   </si>
   <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -351,6 +369,9 @@
     <t>MARCO</t>
   </si>
   <si>
+    <t>PAUL ARAVIER</t>
+  </si>
+  <si>
     <t>JOSE RAMON</t>
   </si>
   <si>
@@ -384,6 +405,9 @@
     <t>FABIAN ALEJANDRO</t>
   </si>
   <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
@@ -396,6 +420,9 @@
     <t>ERIK OMAR</t>
   </si>
   <si>
+    <t>DIEGO IVAN</t>
+  </si>
+  <si>
     <t>VICTOR MANUEL</t>
   </si>
   <si>
@@ -436,33 +463,6 @@
   </si>
   <si>
     <t>YAIR</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>DIEGO IVAN</t>
   </si>
 </sst>
 </file>
@@ -954,7 +954,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>6</v>
@@ -1008,7 +1008,7 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -1060,7 +1060,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -1114,7 +1114,7 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1137,7 +1137,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -1191,7 +1191,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1214,7 +1214,7 @@
         <v>5</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>10</v>
@@ -1268,7 +1268,7 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1291,7 +1291,7 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>5</v>
@@ -1345,7 +1345,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1368,7 +1368,7 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1422,7 +1422,7 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1445,7 +1445,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1499,7 +1499,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1522,7 +1522,7 @@
         <v>8</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -1576,7 +1576,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1599,7 +1599,7 @@
         <v>8</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>8</v>
@@ -1653,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1676,7 +1676,7 @@
         <v>6</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E14">
         <v>8</v>
@@ -1730,7 +1730,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1753,7 +1753,7 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -1807,7 +1807,7 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1830,7 +1830,7 @@
         <v>6</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E16">
         <v>5</v>
@@ -1884,7 +1884,7 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -1907,7 +1907,7 @@
         <v>5</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -1961,7 +1961,7 @@
         <v>5</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2049,7 +2049,7 @@
         <v>5</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -2103,7 +2103,7 @@
         <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>5</v>
@@ -2180,7 +2180,7 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2203,7 +2203,7 @@
         <v>5</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -2257,7 +2257,7 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2280,7 +2280,7 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E22">
         <v>6</v>
@@ -2334,7 +2334,7 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2357,7 +2357,7 @@
         <v>6</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E23">
         <v>6</v>
@@ -2411,7 +2411,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2463,7 +2463,7 @@
         <v>5</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E25">
         <v>5</v>
@@ -2517,7 +2517,7 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2540,7 +2540,7 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>10</v>
@@ -2594,7 +2594,7 @@
         <v>7</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2617,7 +2617,7 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>7</v>
@@ -2671,7 +2671,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2694,7 +2694,7 @@
         <v>5</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -2748,7 +2748,7 @@
         <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -2771,7 +2771,7 @@
         <v>5</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E29">
         <v>5</v>
@@ -2825,7 +2825,7 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -2848,7 +2848,7 @@
         <v>6</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E30">
         <v>6</v>
@@ -2902,7 +2902,7 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -2925,7 +2925,7 @@
         <v>5</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -2979,7 +2979,7 @@
         <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -3002,7 +3002,7 @@
         <v>5</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E32">
         <v>7</v>
@@ -3056,7 +3056,7 @@
         <v>5</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>7</v>
@@ -3079,7 +3079,7 @@
         <v>5</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -3133,7 +3133,7 @@
         <v>5</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W33">
         <v>6</v>
@@ -3156,7 +3156,7 @@
         <v>6</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E34">
         <v>7</v>
@@ -3210,7 +3210,7 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3233,7 +3233,7 @@
         <v>6</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E35">
         <v>8</v>
@@ -3287,7 +3287,7 @@
         <v>6</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3310,7 +3310,7 @@
         <v>5</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E36">
         <v>5</v>
@@ -3364,7 +3364,7 @@
         <v>5</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3497,7 +3497,7 @@
         <v>95</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="E4">
         <v>85</v>
@@ -3579,7 +3579,7 @@
         <v>85</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="E6">
         <v>85</v>
@@ -3638,7 +3638,7 @@
         <v>95</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -3697,7 +3697,7 @@
         <v>80</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -3756,7 +3756,7 @@
         <v>60</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="E9">
         <v>50</v>
@@ -3815,7 +3815,7 @@
         <v>40</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="E10">
         <v>85</v>
@@ -3874,7 +3874,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -3933,7 +3933,7 @@
         <v>95</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -3992,7 +3992,7 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -4051,7 +4051,7 @@
         <v>80</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="E14">
         <v>85</v>
@@ -4110,7 +4110,7 @@
         <v>95</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="E15">
         <v>80</v>
@@ -4169,7 +4169,7 @@
         <v>80</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>95</v>
@@ -4228,7 +4228,7 @@
         <v>60</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>60</v>
@@ -4337,7 +4337,7 @@
         <v>80</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="E19">
         <v>80</v>
@@ -4396,7 +4396,7 @@
         <v>40</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="E20">
         <v>70</v>
@@ -4455,7 +4455,7 @@
         <v>80</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -4514,7 +4514,7 @@
         <v>95</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="E22">
         <v>85</v>
@@ -4573,7 +4573,7 @@
         <v>85</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E23">
         <v>85</v>
@@ -4655,7 +4655,7 @@
         <v>85</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="E25">
         <v>65</v>
@@ -4714,7 +4714,7 @@
         <v>85</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -4773,7 +4773,7 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -4832,7 +4832,7 @@
         <v>50</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="E28">
         <v>70</v>
@@ -4891,7 +4891,7 @@
         <v>85</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E29">
         <v>90</v>
@@ -4950,7 +4950,7 @@
         <v>90</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="E30">
         <v>90</v>
@@ -5009,7 +5009,7 @@
         <v>65</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="E31">
         <v>80</v>
@@ -5068,7 +5068,7 @@
         <v>95</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -5127,7 +5127,7 @@
         <v>60</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="E33">
         <v>100</v>
@@ -5186,7 +5186,7 @@
         <v>80</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E34">
         <v>90</v>
@@ -5245,7 +5245,7 @@
         <v>85</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="E35">
         <v>100</v>
@@ -5304,7 +5304,7 @@
         <v>65</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E36">
         <v>10</v>
@@ -5413,22 +5413,25 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="H2">
+        <v>5.5</v>
       </c>
       <c r="I2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5598,7 +5601,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5623,603 +5626,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920177</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920178</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920179</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920181</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920389</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920183</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920184</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920185</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920188</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920187</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920190</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" t="s">
-        <v>119</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920413</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920388</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920378</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" t="s">
-        <v>122</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920359</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920192</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920193</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920195</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920197</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920358</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920356</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920180</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" t="s">
-        <v>130</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920363</v>
-      </c>
-      <c r="B24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920390</v>
-      </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920199</v>
-      </c>
-      <c r="B26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" t="s">
-        <v>133</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920200</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920371</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" t="s">
-        <v>135</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920201</v>
-      </c>
-      <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920202</v>
-      </c>
-      <c r="B30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920204</v>
-      </c>
-      <c r="B31" t="s">
-        <v>90</v>
-      </c>
-      <c r="C31" t="s">
-        <v>108</v>
-      </c>
-      <c r="D31" t="s">
-        <v>138</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -6261,514 +5667,514 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920178</v>
+        <v>20330051920072</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920179</v>
+        <v>22330051920178</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920181</v>
+        <v>22330051920179</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920389</v>
+        <v>22330051920181</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920183</v>
+        <v>22330051920389</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920184</v>
+        <v>22330051920183</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920185</v>
+        <v>22330051920184</v>
       </c>
       <c r="B9" t="s">
         <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920188</v>
+        <v>22330051920185</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920187</v>
+        <v>22330051920188</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920190</v>
+        <v>22330051920187</v>
       </c>
       <c r="B12" t="s">
         <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920413</v>
+        <v>22330051920190</v>
       </c>
       <c r="B13" t="s">
         <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920388</v>
+        <v>22330051920413</v>
       </c>
       <c r="B14" t="s">
         <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920378</v>
+        <v>21330051920014</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920359</v>
+        <v>22330051920388</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920192</v>
+        <v>22330051920378</v>
       </c>
       <c r="B17" t="s">
         <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920193</v>
+        <v>22330051920359</v>
       </c>
       <c r="B18" t="s">
         <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920195</v>
+        <v>22330051920192</v>
       </c>
       <c r="B19" t="s">
         <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920197</v>
+        <v>20330051920090</v>
       </c>
       <c r="B20" t="s">
         <v>80</v>
       </c>
+      <c r="C20" t="s">
+        <v>107</v>
+      </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920358</v>
+        <v>22330051920193</v>
       </c>
       <c r="B21" t="s">
         <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920356</v>
+        <v>22330051920195</v>
       </c>
       <c r="B22" t="s">
         <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920180</v>
+        <v>22330051920197</v>
       </c>
       <c r="B23" t="s">
         <v>83</v>
       </c>
-      <c r="C23" t="s">
-        <v>72</v>
-      </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920363</v>
+        <v>22330051920358</v>
       </c>
       <c r="B24" t="s">
         <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920390</v>
+        <v>22330051920356</v>
       </c>
       <c r="B25" t="s">
         <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920199</v>
+        <v>22330051920180</v>
       </c>
       <c r="B26" t="s">
         <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920200</v>
+        <v>22330051920363</v>
       </c>
       <c r="B27" t="s">
         <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920371</v>
+        <v>22330051920390</v>
       </c>
       <c r="B28" t="s">
         <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920201</v>
+        <v>22330051920199</v>
       </c>
       <c r="B29" t="s">
         <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920202</v>
+        <v>22330051920200</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920204</v>
+        <v>22330051920371</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920072</v>
+        <v>22330051920201</v>
       </c>
       <c r="B32" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -6779,13 +6185,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920014</v>
+        <v>22330051920202</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -6796,13 +6202,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920090</v>
+        <v>22330051920204</v>
       </c>
       <c r="B34" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
         <v>147</v>
@@ -6818,7 +6224,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6850,39 +6256,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920184</v>
+        <v>22330051920180</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920184</v>
+        <v>22330051920180</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6896,16 +6302,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920378</v>
+        <v>22330051920371</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6919,16 +6325,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920378</v>
+        <v>22330051920371</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -6937,27 +6343,27 @@
         <v>57</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920200</v>
+        <v>22330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6965,45 +6371,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920200</v>
+        <v>22330051920202</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920371</v>
+        <v>22330051920177</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7011,68 +6417,68 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920371</v>
+        <v>20330051920072</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920202</v>
+        <v>22330051920184</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920202</v>
+        <v>22330051920188</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7080,16 +6486,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920177</v>
+        <v>22330051920187</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -7098,27 +6504,27 @@
         <v>57</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920072</v>
+        <v>22330051920378</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7126,16 +6532,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920179</v>
+        <v>22330051920192</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -7144,44 +6550,44 @@
         <v>57</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920183</v>
+        <v>20330051920090</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920185</v>
+        <v>22330051920363</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -7190,165 +6596,30 @@
         <v>57</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920188</v>
+        <v>22330051920200</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920187</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920192</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920090</v>
-      </c>
-      <c r="B20" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" t="s">
-        <v>147</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920197</v>
-      </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" t="s">
-        <v>127</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920358</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" t="s">
-        <v>128</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920363</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2AEV - Estadisticos 20222.xlsx
+++ b/grupos/2AEV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -198,7 +198,10 @@
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
@@ -5503,7 +5506,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5">
         <v>33</v>
@@ -5535,7 +5538,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>31</v>
@@ -5567,7 +5570,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7">
         <v>31</v>
@@ -5610,16 +5613,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5644,16 +5647,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>55</v>
@@ -5664,13 +5667,13 @@
         <v>22330051920177</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5681,13 +5684,13 @@
         <v>20330051920072</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -5698,13 +5701,13 @@
         <v>22330051920178</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -5715,13 +5718,13 @@
         <v>22330051920179</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -5732,13 +5735,13 @@
         <v>22330051920181</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5749,13 +5752,13 @@
         <v>22330051920389</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5766,13 +5769,13 @@
         <v>22330051920183</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5783,13 +5786,13 @@
         <v>22330051920184</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5800,13 +5803,13 @@
         <v>22330051920185</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -5817,13 +5820,13 @@
         <v>22330051920188</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5834,13 +5837,13 @@
         <v>22330051920187</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -5851,13 +5854,13 @@
         <v>22330051920190</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5868,13 +5871,13 @@
         <v>22330051920413</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -5885,13 +5888,13 @@
         <v>21330051920014</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5902,13 +5905,13 @@
         <v>22330051920388</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5919,13 +5922,13 @@
         <v>22330051920378</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5936,13 +5939,13 @@
         <v>22330051920359</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5953,13 +5956,13 @@
         <v>22330051920192</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5970,13 +5973,13 @@
         <v>20330051920090</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5987,13 +5990,13 @@
         <v>22330051920193</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6004,13 +6007,13 @@
         <v>22330051920195</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6021,10 +6024,10 @@
         <v>22330051920197</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6035,13 +6038,13 @@
         <v>22330051920358</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6052,13 +6055,13 @@
         <v>22330051920356</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6069,13 +6072,13 @@
         <v>22330051920180</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6086,13 +6089,13 @@
         <v>22330051920363</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6103,13 +6106,13 @@
         <v>22330051920390</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6120,13 +6123,13 @@
         <v>22330051920199</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6137,13 +6140,13 @@
         <v>22330051920200</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6154,13 +6157,13 @@
         <v>22330051920371</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6171,13 +6174,13 @@
         <v>22330051920201</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6188,13 +6191,13 @@
         <v>22330051920202</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -6205,13 +6208,13 @@
         <v>22330051920204</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -6233,16 +6236,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6259,13 +6262,13 @@
         <v>22330051920180</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6282,13 +6285,13 @@
         <v>22330051920180</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6305,13 +6308,13 @@
         <v>22330051920371</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6328,13 +6331,13 @@
         <v>22330051920371</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -6351,13 +6354,13 @@
         <v>22330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -6374,13 +6377,13 @@
         <v>22330051920202</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -6397,13 +6400,13 @@
         <v>22330051920177</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -6420,13 +6423,13 @@
         <v>20330051920072</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6443,13 +6446,13 @@
         <v>22330051920184</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -6466,13 +6469,13 @@
         <v>22330051920188</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -6489,13 +6492,13 @@
         <v>22330051920187</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -6512,13 +6515,13 @@
         <v>22330051920378</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -6535,13 +6538,13 @@
         <v>22330051920192</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -6558,19 +6561,19 @@
         <v>20330051920090</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -6581,13 +6584,13 @@
         <v>22330051920363</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -6604,13 +6607,13 @@
         <v>22330051920200</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>

--- a/grupos/2AEV - Estadisticos 20222.xlsx
+++ b/grupos/2AEV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -222,151 +221,73 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>PUGA CABRERA</t>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TZOMPOLE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>CAZARES</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
+    <t>DIEGO IVAN</t>
+  </si>
+  <si>
+    <t>ABDIEL NOE</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>ERIK</t>
   </si>
   <si>
     <t>MARCO</t>
@@ -375,103 +296,31 @@
     <t>PAUL ARAVIER</t>
   </si>
   <si>
-    <t>JOSE RAMON</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>GERSON</t>
-  </si>
-  <si>
-    <t>LEONEL FELIPE</t>
-  </si>
-  <si>
-    <t>LUIS DAVID</t>
-  </si>
-  <si>
     <t>DAVID</t>
   </si>
   <si>
     <t>HECTOR ALAN</t>
   </si>
   <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
     <t>JAIRO YAIR</t>
   </si>
   <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
     <t>ERIK OMAR</t>
   </si>
   <si>
-    <t>DIEGO IVAN</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>JESUS IVAN</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
     <t>OSMAR</t>
   </si>
   <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO</t>
-  </si>
-  <si>
     <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>YAIR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -524,11 +373,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -984,7 +834,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1020,7 +870,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1037,7 +887,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1090,7 +940,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1167,7 +1017,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1244,7 +1094,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1321,7 +1171,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1357,7 +1207,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1398,7 +1248,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1475,7 +1325,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1552,7 +1402,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1588,7 +1438,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1629,7 +1479,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1706,7 +1556,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1783,7 +1633,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1860,7 +1710,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1937,7 +1787,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2008,7 +1858,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2079,7 +1929,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2156,7 +2006,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2233,7 +2083,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2269,7 +2119,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2310,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2346,7 +2196,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2387,7 +2237,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2440,7 +2290,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2452,7 +2302,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2493,7 +2343,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2570,7 +2420,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2647,7 +2497,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2724,7 +2574,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2801,7 +2651,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2878,7 +2728,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2955,7 +2805,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3032,7 +2882,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3109,7 +2959,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3145,7 +2995,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3186,7 +3036,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3263,7 +3113,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3340,7 +3190,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3527,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -3562,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>109.1</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3609,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>114.5</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3668,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3727,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3786,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>63.6</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -3845,7 +3695,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>109.1</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -3904,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -3963,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>114.5</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4022,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4081,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4140,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4199,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4258,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>114.5</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4311,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4367,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>114.5</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4426,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -4485,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4544,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -4603,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>114.5</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -4638,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>101.8</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -4685,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>101.8</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -4744,7 +4594,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -4803,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -4862,7 +4712,7 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>101.8</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -4921,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -4980,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5039,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>101.8</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5098,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5157,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5216,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5275,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -5334,7 +5184,7 @@
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>109.1</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -5371,6 +5221,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5421,10 +5273,10 @@
       <c r="E2">
         <v>21</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>30</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>70</v>
       </c>
       <c r="H2">
@@ -5433,7 +5285,7 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5448,16 +5300,16 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>45.45</v>
-      </c>
-      <c r="G3">
-        <v>54.55</v>
+        <v>19</v>
+      </c>
+      <c r="F3" s="2">
+        <v>42.4</v>
+      </c>
+      <c r="G3" s="2">
+        <v>57.6</v>
       </c>
       <c r="H3">
         <v>6.1</v>
@@ -5465,7 +5317,7 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5485,11 +5337,11 @@
       <c r="E4">
         <v>16</v>
       </c>
-      <c r="F4">
-        <v>48.39</v>
-      </c>
-      <c r="G4">
-        <v>51.61</v>
+      <c r="F4" s="2">
+        <v>48.4</v>
+      </c>
+      <c r="G4" s="2">
+        <v>51.6</v>
       </c>
       <c r="H4">
         <v>5.8</v>
@@ -5497,7 +5349,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5517,11 +5369,11 @@
       <c r="E5">
         <v>14</v>
       </c>
-      <c r="F5">
-        <v>57.58</v>
-      </c>
-      <c r="G5">
-        <v>42.42</v>
+      <c r="F5" s="2">
+        <v>57.6</v>
+      </c>
+      <c r="G5" s="2">
+        <v>42.4</v>
       </c>
       <c r="H5">
         <v>6.8</v>
@@ -5529,7 +5381,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5549,11 +5401,11 @@
       <c r="E6">
         <v>11</v>
       </c>
-      <c r="F6">
-        <v>64.52</v>
-      </c>
-      <c r="G6">
-        <v>35.48</v>
+      <c r="F6" s="2">
+        <v>64.5</v>
+      </c>
+      <c r="G6" s="2">
+        <v>35.5</v>
       </c>
       <c r="H6">
         <v>6.6</v>
@@ -5561,7 +5413,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5581,11 +5433,11 @@
       <c r="E7">
         <v>9</v>
       </c>
-      <c r="F7">
-        <v>70.97</v>
-      </c>
-      <c r="G7">
-        <v>29.03</v>
+      <c r="F7" s="2">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2">
+        <v>29</v>
       </c>
       <c r="H7">
         <v>6.9</v>
@@ -5593,7 +5445,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5638,595 +5490,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22330051920177</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>20330051920072</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>22330051920178</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>22330051920179</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>22330051920181</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>22330051920389</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>22330051920183</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>22330051920184</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>22330051920185</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" t="s">
-        <v>124</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>22330051920188</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" t="s">
-        <v>125</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>22330051920187</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>22330051920190</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>22330051920413</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>128</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>21330051920014</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>22330051920388</v>
-      </c>
-      <c r="B16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" t="s">
-        <v>130</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>22330051920378</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>22330051920359</v>
-      </c>
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>22330051920192</v>
-      </c>
-      <c r="B19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" t="s">
-        <v>133</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>20330051920090</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" t="s">
-        <v>134</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>22330051920193</v>
-      </c>
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" t="s">
-        <v>135</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>22330051920195</v>
-      </c>
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>22330051920197</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>22330051920358</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" t="s">
-        <v>138</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>22330051920356</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>22330051920180</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" t="s">
-        <v>140</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>22330051920363</v>
-      </c>
-      <c r="B27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" t="s">
-        <v>141</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>22330051920390</v>
-      </c>
-      <c r="B28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" t="s">
-        <v>142</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>22330051920199</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>114</v>
-      </c>
-      <c r="D29" t="s">
-        <v>143</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>22330051920200</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" t="s">
-        <v>144</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>22330051920371</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" t="s">
-        <v>145</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>22330051920201</v>
-      </c>
-      <c r="B32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" t="s">
-        <v>146</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>22330051920202</v>
-      </c>
-      <c r="B33" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" t="s">
-        <v>114</v>
-      </c>
-      <c r="D33" t="s">
-        <v>147</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>22330051920204</v>
-      </c>
-      <c r="B34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" t="s">
-        <v>115</v>
-      </c>
-      <c r="D34" t="s">
-        <v>148</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6259,22 +5522,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920180</v>
+        <v>20330051920090</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6282,16 +5545,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920180</v>
+        <v>20330051920090</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6305,16 +5568,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920371</v>
+        <v>22330051920180</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6328,22 +5591,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920371</v>
+        <v>22330051920180</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
         <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6351,22 +5614,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920202</v>
+        <v>22330051920371</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6374,22 +5637,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920202</v>
+        <v>22330051920371</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6397,16 +5660,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920177</v>
+        <v>22330051920202</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -6420,16 +5683,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920072</v>
+        <v>22330051920202</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6443,22 +5706,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920184</v>
+        <v>22330051920177</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6466,22 +5729,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920188</v>
+        <v>20330051920072</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6489,16 +5752,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920187</v>
+        <v>22330051920188</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -6512,22 +5775,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920378</v>
+        <v>22330051920187</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6535,22 +5798,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920192</v>
+        <v>22330051920378</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6558,22 +5821,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920090</v>
+        <v>22330051920192</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -6584,13 +5847,13 @@
         <v>22330051920363</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -6607,13 +5870,13 @@
         <v>22330051920200</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>

--- a/grupos/2AEV - Estadisticos 20222.xlsx
+++ b/grupos/2AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="93">
   <si>
     <t>Materia</t>
   </si>
@@ -194,15 +194,15 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
@@ -221,13 +221,16 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>VERA</t>
+    <t>VASQUEZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
@@ -236,12 +239,6 @@
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -251,40 +248,37 @@
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>BAROJAS</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>COLOHUA</t>
   </si>
   <si>
     <t>CABRERA</t>
   </si>
   <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>ROSAS</t>
   </si>
   <si>
     <t>PLIEGO</t>
   </si>
   <si>
+    <t>PAUL ARAVIER</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
     <t>DIEGO IVAN</t>
   </si>
   <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
+    <t>NAHUM HIRAM</t>
   </si>
   <si>
     <t>ERIK</t>
@@ -293,12 +287,6 @@
     <t>MARCO</t>
   </si>
   <si>
-    <t>PAUL ARAVIER</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
     <t>HECTOR ALAN</t>
   </si>
   <si>
@@ -309,9 +297,6 @@
   </si>
   <si>
     <t>OSMAR</t>
-  </si>
-  <si>
-    <t>NAHUM HIRAM</t>
   </si>
 </sst>
 </file>
@@ -819,10 +804,10 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -831,7 +816,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -855,7 +840,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>6</v>
@@ -884,7 +869,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -896,7 +881,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -925,10 +910,10 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -937,7 +922,7 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -961,7 +946,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -973,7 +958,7 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1002,10 +987,10 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1014,7 +999,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -1038,10 +1023,10 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1050,7 +1035,7 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1079,10 +1064,10 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1091,7 +1076,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>6</v>
@@ -1115,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -1156,10 +1141,10 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1168,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>4</v>
@@ -1233,10 +1218,10 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1245,7 +1230,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>5</v>
@@ -1310,10 +1295,10 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1322,7 +1307,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -1358,7 +1343,7 @@
         <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1387,10 +1372,10 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1399,7 +1384,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>8</v>
@@ -1423,7 +1408,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1464,10 +1449,10 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1476,7 +1461,7 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>9</v>
@@ -1541,10 +1526,10 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1553,7 +1538,7 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>7</v>
@@ -1577,10 +1562,10 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1618,10 +1603,10 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1630,7 +1615,7 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -1657,7 +1642,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -1695,10 +1680,10 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1707,7 +1692,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -1734,7 +1719,7 @@
         <v>5</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -1772,10 +1757,10 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -1784,7 +1769,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>6</v>
@@ -1846,16 +1831,16 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -1914,10 +1899,10 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -1926,7 +1911,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -1991,10 +1976,10 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2003,7 +1988,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -2068,10 +2053,10 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2080,7 +2065,7 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2104,7 +2089,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -2116,7 +2101,7 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2145,10 +2130,10 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2157,7 +2142,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -2181,7 +2166,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2222,10 +2207,10 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2234,7 +2219,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2258,10 +2243,10 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2287,7 +2272,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2328,10 +2313,10 @@
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2340,7 +2325,7 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>5</v>
@@ -2405,10 +2390,10 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2417,7 +2402,7 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>7</v>
@@ -2441,7 +2426,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -2453,7 +2438,7 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2482,10 +2467,10 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2494,7 +2479,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
         <v>7</v>
@@ -2530,7 +2515,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2559,10 +2544,10 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2571,7 +2556,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>5</v>
@@ -2607,7 +2592,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -2636,10 +2621,10 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -2648,7 +2633,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>5</v>
@@ -2713,10 +2698,10 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -2725,7 +2710,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>7</v>
@@ -2749,7 +2734,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>6</v>
@@ -2790,10 +2775,10 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>-1</v>
@@ -2802,7 +2787,7 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>5</v>
@@ -2867,10 +2852,10 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -2879,7 +2864,7 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>6</v>
@@ -2903,7 +2888,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -2944,10 +2929,10 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -2956,7 +2941,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>9</v>
@@ -2980,7 +2965,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>5</v>
@@ -2992,7 +2977,7 @@
         <v>6</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>8</v>
@@ -3021,10 +3006,10 @@
         <v>5</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3033,7 +3018,7 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>5</v>
@@ -3060,7 +3045,7 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -3098,10 +3083,10 @@
         <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3110,7 +3095,7 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M35">
         <v>6</v>
@@ -3134,7 +3119,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>6</v>
@@ -3175,10 +3160,10 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -3187,7 +3172,7 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>5</v>
@@ -3362,10 +3347,10 @@
         <v>101.8</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3374,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M4">
         <v>116.4</v>
@@ -3409,7 +3394,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="M5">
         <v>109.1</v>
@@ -3444,10 +3429,10 @@
         <v>98.2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3456,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M6">
         <v>114.5</v>
@@ -3503,10 +3488,10 @@
         <v>109.1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3515,7 +3500,7 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>120</v>
@@ -3562,10 +3547,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3574,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M8">
         <v>116.4</v>
@@ -3624,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3633,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M9">
         <v>63.6</v>
@@ -3680,10 +3665,10 @@
         <v>85.5</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3692,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M10">
         <v>109.1</v>
@@ -3739,10 +3724,10 @@
         <v>109.1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3751,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>116.4</v>
@@ -3798,10 +3783,10 @@
         <v>87.3</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3810,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M12">
         <v>114.5</v>
@@ -3857,10 +3842,10 @@
         <v>109.1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3869,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>120</v>
@@ -3916,10 +3901,10 @@
         <v>109.1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3928,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M14">
         <v>116.4</v>
@@ -3975,10 +3960,10 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3987,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M15">
         <v>120</v>
@@ -4034,10 +4019,10 @@
         <v>109.1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4046,7 +4031,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M16">
         <v>116.4</v>
@@ -4093,10 +4078,10 @@
         <v>85.5</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4105,7 +4090,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M17">
         <v>114.5</v>
@@ -4149,16 +4134,16 @@
         <v>74.5</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M18">
         <v>83.59999999999999</v>
@@ -4202,10 +4187,10 @@
         <v>85.5</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4214,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>114.5</v>
@@ -4264,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4273,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M20">
         <v>83.59999999999999</v>
@@ -4320,10 +4305,10 @@
         <v>109.1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4332,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
         <v>120</v>
@@ -4379,10 +4364,10 @@
         <v>109.1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4391,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M22">
         <v>116.4</v>
@@ -4438,10 +4423,10 @@
         <v>103.6</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4450,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M23">
         <v>114.5</v>
@@ -4520,10 +4505,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4532,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M25">
         <v>101.8</v>
@@ -4579,10 +4564,10 @@
         <v>109.1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4591,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M26">
         <v>120</v>
@@ -4638,10 +4623,10 @@
         <v>109.1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4650,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>120</v>
@@ -4697,10 +4682,10 @@
         <v>87.3</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4709,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M28">
         <v>101.8</v>
@@ -4756,10 +4741,10 @@
         <v>94.5</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4768,7 +4753,7 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M29">
         <v>116.4</v>
@@ -4815,10 +4800,10 @@
         <v>98.2</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4827,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M30">
         <v>116.4</v>
@@ -4874,10 +4859,10 @@
         <v>63.6</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4886,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M31">
         <v>101.8</v>
@@ -4933,10 +4918,10 @@
         <v>109.1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4945,7 +4930,7 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>120</v>
@@ -4992,10 +4977,10 @@
         <v>105.5</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -5004,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M33">
         <v>120</v>
@@ -5051,10 +5036,10 @@
         <v>109.1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -5063,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34">
         <v>116.4</v>
@@ -5110,10 +5095,10 @@
         <v>92.7</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -5122,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35">
         <v>116.4</v>
@@ -5169,10 +5154,10 @@
         <v>63.6</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -5181,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M36">
         <v>109.1</v>
@@ -5291,28 +5276,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2">
-        <v>42.4</v>
+        <v>35.5</v>
       </c>
       <c r="G3" s="2">
-        <v>57.6</v>
+        <v>64.5</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5323,28 +5308,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2">
-        <v>48.4</v>
+        <v>42.4</v>
       </c>
       <c r="G4" s="2">
-        <v>51.6</v>
+        <v>57.6</v>
       </c>
       <c r="H4">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5355,7 +5340,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -5364,19 +5349,19 @@
         <v>33</v>
       </c>
       <c r="D5">
+        <v>14</v>
+      </c>
+      <c r="E5">
         <v>19</v>
       </c>
-      <c r="E5">
-        <v>14</v>
-      </c>
       <c r="F5" s="2">
+        <v>42.4</v>
+      </c>
+      <c r="G5" s="2">
         <v>57.6</v>
       </c>
-      <c r="G5" s="2">
-        <v>42.4</v>
-      </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5396,19 +5381,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="2">
-        <v>64.5</v>
+        <v>61.3</v>
       </c>
       <c r="G6" s="2">
-        <v>35.5</v>
+        <v>38.7</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5490,7 +5475,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5522,22 +5507,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920090</v>
+        <v>20330051920072</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5545,22 +5530,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920090</v>
+        <v>20330051920072</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5568,22 +5553,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920180</v>
+        <v>22330051920188</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5591,22 +5576,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920180</v>
+        <v>22330051920188</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5614,19 +5599,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920371</v>
+        <v>20330051920090</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>59</v>
@@ -5637,22 +5622,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920371</v>
+        <v>20330051920090</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5660,22 +5645,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920202</v>
+        <v>22330051920200</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5683,19 +5668,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920202</v>
+        <v>22330051920200</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>58</v>
@@ -5706,16 +5691,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920177</v>
+        <v>22330051920202</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5729,22 +5714,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920072</v>
+        <v>22330051920202</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5752,16 +5737,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920188</v>
+        <v>22330051920177</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -5778,13 +5763,13 @@
         <v>22330051920187</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -5801,19 +5786,19 @@
         <v>22330051920378</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5824,13 +5809,13 @@
         <v>22330051920192</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -5847,13 +5832,13 @@
         <v>22330051920363</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -5862,29 +5847,6 @@
         <v>57</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920200</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" t="s">
-        <v>97</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2AEV - Estadisticos 20222.xlsx
+++ b/grupos/2AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -203,12 +203,12 @@
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -263,9 +263,6 @@
     <t>CABRERA</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
@@ -285,9 +282,6 @@
   </si>
   <si>
     <t>MARCO</t>
-  </si>
-  <si>
-    <t>HECTOR ALAN</t>
   </si>
   <si>
     <t>JAIRO YAIR</t>
@@ -810,10 +804,10 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -916,10 +910,10 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -955,7 +949,7 @@
         <v>5</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -993,10 +987,10 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1029,7 +1023,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1070,10 +1064,10 @@
         <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>8</v>
@@ -1106,7 +1100,7 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1147,10 +1141,10 @@
         <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -1224,10 +1218,10 @@
         <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -1301,10 +1295,10 @@
         <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -1378,10 +1372,10 @@
         <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1414,7 +1408,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1455,10 +1449,10 @@
         <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1491,7 +1485,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1532,10 +1526,10 @@
         <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -1571,7 +1565,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1609,10 +1603,10 @@
         <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -1645,10 +1639,10 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1686,10 +1680,10 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>6</v>
@@ -1763,10 +1757,10 @@
         <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -1837,7 +1831,7 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -1905,10 +1899,10 @@
         <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -1982,10 +1976,10 @@
         <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -2059,10 +2053,10 @@
         <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2095,7 +2089,7 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2136,10 +2130,10 @@
         <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -2213,10 +2207,10 @@
         <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>5</v>
@@ -2252,7 +2246,7 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2319,10 +2313,10 @@
         <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -2396,10 +2390,10 @@
         <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -2432,7 +2426,7 @@
         <v>7</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2473,10 +2467,10 @@
         <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>7</v>
@@ -2509,7 +2503,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2550,10 +2544,10 @@
         <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>6</v>
@@ -2627,10 +2621,10 @@
         <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -2704,10 +2698,10 @@
         <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>7</v>
@@ -2781,10 +2775,10 @@
         <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -2820,7 +2814,7 @@
         <v>5</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
         <v>5</v>
@@ -2858,10 +2852,10 @@
         <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>7</v>
@@ -2935,10 +2929,10 @@
         <v>5</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -2974,7 +2968,7 @@
         <v>5</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X33">
         <v>6</v>
@@ -3012,10 +3006,10 @@
         <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -3089,10 +3083,10 @@
         <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>6</v>
@@ -3128,7 +3122,7 @@
         <v>5</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>6</v>
@@ -3166,10 +3160,10 @@
         <v>5</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
         <v>6</v>
@@ -3353,10 +3347,10 @@
         <v>85</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>90</v>
@@ -3435,10 +3429,10 @@
         <v>80</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L6">
         <v>85</v>
@@ -3494,10 +3488,10 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3553,10 +3547,10 @@
         <v>75</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>95</v>
@@ -3671,10 +3665,10 @@
         <v>50</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L10">
         <v>80</v>
@@ -3730,10 +3724,10 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -3789,10 +3783,10 @@
         <v>95</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>95</v>
@@ -3848,10 +3842,10 @@
         <v>90</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -3907,10 +3901,10 @@
         <v>75</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L14">
         <v>90</v>
@@ -3966,10 +3960,10 @@
         <v>85</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L15">
         <v>95</v>
@@ -4025,10 +4019,10 @@
         <v>75</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L16">
         <v>90</v>
@@ -4084,10 +4078,10 @@
         <v>60</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L17">
         <v>95</v>
@@ -4140,7 +4134,7 @@
         <v>75</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L18">
         <v>80</v>
@@ -4193,10 +4187,10 @@
         <v>80</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -4311,10 +4305,10 @@
         <v>90</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -4370,10 +4364,10 @@
         <v>85</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L22">
         <v>90</v>
@@ -4429,10 +4423,10 @@
         <v>75</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L23">
         <v>80</v>
@@ -4511,10 +4505,10 @@
         <v>75</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L25">
         <v>80</v>
@@ -4570,10 +4564,10 @@
         <v>80</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>90</v>
@@ -4629,10 +4623,10 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -4688,10 +4682,10 @@
         <v>60</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L28">
         <v>90</v>
@@ -4747,10 +4741,10 @@
         <v>75</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L29">
         <v>75</v>
@@ -4806,10 +4800,10 @@
         <v>85</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L30">
         <v>90</v>
@@ -4865,10 +4859,10 @@
         <v>85</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L31">
         <v>80</v>
@@ -4924,10 +4918,10 @@
         <v>90</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -4983,10 +4977,10 @@
         <v>60</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L33">
         <v>80</v>
@@ -5042,10 +5036,10 @@
         <v>100</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -5101,10 +5095,10 @@
         <v>100</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -5160,10 +5154,10 @@
         <v>65</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L36">
         <v>85</v>
@@ -5253,19 +5247,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="G2" s="2">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5372,7 +5366,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -5381,16 +5375,16 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2">
-        <v>61.3</v>
+        <v>58.1</v>
       </c>
       <c r="G6" s="2">
-        <v>38.7</v>
+        <v>41.9</v>
       </c>
       <c r="H6">
         <v>6.7</v>
@@ -5404,7 +5398,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -5413,19 +5407,19 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F7" s="2">
-        <v>71</v>
+        <v>61.3</v>
       </c>
       <c r="G7" s="2">
-        <v>29</v>
+        <v>38.7</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5475,7 +5469,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5516,7 +5510,7 @@
         <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5539,7 +5533,7 @@
         <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5562,7 +5556,7 @@
         <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5585,7 +5579,7 @@
         <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5608,7 +5602,7 @@
         <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5631,7 +5625,7 @@
         <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5654,7 +5648,7 @@
         <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5677,7 +5671,7 @@
         <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5700,7 +5694,7 @@
         <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5723,7 +5717,7 @@
         <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5746,7 +5740,7 @@
         <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -5760,22 +5754,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920187</v>
+        <v>22330051920378</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
         <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5783,22 +5777,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920378</v>
+        <v>22330051920192</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5806,16 +5800,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920192</v>
+        <v>22330051920363</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -5824,29 +5818,6 @@
         <v>57</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920363</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2AEV - Estadisticos 20222.xlsx
+++ b/grupos/2AEV - Estadisticos 20222.xlsx
@@ -3329,7 +3329,7 @@
         <v>95</v>
       </c>
       <c r="D4">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="E4">
         <v>85</v>
@@ -3338,43 +3338,43 @@
         <v>90</v>
       </c>
       <c r="G4">
-        <v>101.8</v>
+        <v>93.3</v>
       </c>
       <c r="H4">
-        <v>80</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J4">
-        <v>86.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="L4">
         <v>90</v>
       </c>
       <c r="M4">
-        <v>116.4</v>
+        <v>95.2</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3385,19 +3385,19 @@
         <v>93.3</v>
       </c>
       <c r="G5">
-        <v>96.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="H5">
-        <v>73.3</v>
+        <v>86.2</v>
       </c>
       <c r="M5">
-        <v>109.1</v>
+        <v>89.7</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>86.2</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3411,7 +3411,7 @@
         <v>85</v>
       </c>
       <c r="D6">
-        <v>86.7</v>
+        <v>81.3</v>
       </c>
       <c r="E6">
         <v>85</v>
@@ -3420,43 +3420,43 @@
         <v>95</v>
       </c>
       <c r="G6">
-        <v>98.2</v>
+        <v>90</v>
       </c>
       <c r="H6">
-        <v>73.3</v>
+        <v>86.2</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="J6">
-        <v>86.7</v>
+        <v>81.3</v>
       </c>
       <c r="K6">
         <v>85</v>
       </c>
       <c r="L6">
+        <v>90</v>
+      </c>
+      <c r="M6">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="N6">
+        <v>86.2</v>
+      </c>
+      <c r="O6">
+        <v>82.5</v>
+      </c>
+      <c r="P6">
+        <v>81.3</v>
+      </c>
+      <c r="Q6">
         <v>85</v>
       </c>
-      <c r="M6">
-        <v>114.5</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
       <c r="R6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3470,7 +3470,7 @@
         <v>95</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -3479,16 +3479,16 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J7">
-        <v>106.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -3497,25 +3497,25 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3529,7 +3529,7 @@
         <v>80</v>
       </c>
       <c r="D8">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -3538,43 +3538,43 @@
         <v>90</v>
       </c>
       <c r="G8">
-        <v>90.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="H8">
-        <v>73.3</v>
+        <v>79.3</v>
       </c>
       <c r="I8">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="M8">
-        <v>116.4</v>
+        <v>90.5</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>79.3</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3588,7 +3588,7 @@
         <v>60</v>
       </c>
       <c r="D9">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="E9">
         <v>50</v>
@@ -3597,43 +3597,43 @@
         <v>80</v>
       </c>
       <c r="G9">
-        <v>69.09999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>41.4</v>
       </c>
       <c r="I9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L9">
         <v>80</v>
       </c>
       <c r="M9">
-        <v>63.6</v>
+        <v>57.9</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>41.4</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3647,7 +3647,7 @@
         <v>40</v>
       </c>
       <c r="D10">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="E10">
         <v>85</v>
@@ -3656,43 +3656,43 @@
         <v>95</v>
       </c>
       <c r="G10">
-        <v>85.5</v>
+        <v>78.3</v>
       </c>
       <c r="H10">
-        <v>26.7</v>
+        <v>31</v>
       </c>
       <c r="I10">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J10">
-        <v>93.3</v>
+        <v>75</v>
       </c>
       <c r="K10">
         <v>85</v>
       </c>
       <c r="L10">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="M10">
-        <v>109.1</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3706,7 +3706,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -3715,16 +3715,16 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>100</v>
       </c>
       <c r="J11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3733,25 +3733,25 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>116.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3765,7 +3765,7 @@
         <v>95</v>
       </c>
       <c r="D12">
-        <v>86.7</v>
+        <v>81.3</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -3774,43 +3774,43 @@
         <v>90</v>
       </c>
       <c r="G12">
-        <v>87.3</v>
+        <v>80</v>
       </c>
       <c r="H12">
-        <v>73.3</v>
+        <v>86.2</v>
       </c>
       <c r="I12">
         <v>95</v>
       </c>
       <c r="J12">
-        <v>106.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
+        <v>92.5</v>
+      </c>
+      <c r="M12">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="N12">
+        <v>86.2</v>
+      </c>
+      <c r="O12">
         <v>95</v>
       </c>
-      <c r="M12">
-        <v>114.5</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
       <c r="P12">
-        <v>0</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3824,7 +3824,7 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -3833,16 +3833,16 @@
         <v>100</v>
       </c>
       <c r="G13">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H13">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="I13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -3851,25 +3851,25 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3883,7 +3883,7 @@
         <v>80</v>
       </c>
       <c r="D14">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="E14">
         <v>85</v>
@@ -3892,16 +3892,16 @@
         <v>90</v>
       </c>
       <c r="G14">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>80</v>
+        <v>89.7</v>
       </c>
       <c r="I14">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="J14">
-        <v>106.7</v>
+        <v>93.8</v>
       </c>
       <c r="K14">
         <v>85</v>
@@ -3910,25 +3910,25 @@
         <v>90</v>
       </c>
       <c r="M14">
-        <v>116.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>89.7</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3942,7 +3942,7 @@
         <v>95</v>
       </c>
       <c r="D15">
-        <v>73.3</v>
+        <v>68.8</v>
       </c>
       <c r="E15">
         <v>80</v>
@@ -3951,43 +3951,43 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="H15">
-        <v>86.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I15">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="K15">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="L15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M15">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>81.3</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4001,7 +4001,7 @@
         <v>80</v>
       </c>
       <c r="D16">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="E16">
         <v>95</v>
@@ -4010,43 +4010,43 @@
         <v>100</v>
       </c>
       <c r="G16">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H16">
-        <v>73.3</v>
+        <v>86.2</v>
       </c>
       <c r="I16">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="J16">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K16">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="L16">
+        <v>95</v>
+      </c>
+      <c r="M16">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="N16">
+        <v>86.2</v>
+      </c>
+      <c r="O16">
+        <v>77.5</v>
+      </c>
+      <c r="P16">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Q16">
         <v>90</v>
       </c>
-      <c r="M16">
-        <v>116.4</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
       <c r="R16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4060,7 +4060,7 @@
         <v>60</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="E17">
         <v>60</v>
@@ -4069,43 +4069,43 @@
         <v>85</v>
       </c>
       <c r="G17">
-        <v>85.5</v>
+        <v>78.3</v>
       </c>
       <c r="H17">
-        <v>73.3</v>
+        <v>79.3</v>
       </c>
       <c r="I17">
         <v>60</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="K17">
-        <v>85</v>
+        <v>72.5</v>
       </c>
       <c r="L17">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M17">
-        <v>114.5</v>
+        <v>87.3</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>79.3</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4125,37 +4125,37 @@
         <v>85</v>
       </c>
       <c r="G18">
-        <v>74.5</v>
+        <v>68.3</v>
       </c>
       <c r="H18">
-        <v>46.7</v>
+        <v>63.8</v>
       </c>
       <c r="I18">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K18">
-        <v>15</v>
+        <v>37.5</v>
       </c>
       <c r="L18">
+        <v>82.5</v>
+      </c>
+      <c r="M18">
+        <v>69</v>
+      </c>
+      <c r="N18">
+        <v>63.8</v>
+      </c>
+      <c r="O18">
         <v>80</v>
       </c>
-      <c r="M18">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
       <c r="Q18">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4169,7 +4169,7 @@
         <v>80</v>
       </c>
       <c r="D19">
-        <v>73.3</v>
+        <v>68.8</v>
       </c>
       <c r="E19">
         <v>80</v>
@@ -4178,43 +4178,43 @@
         <v>95</v>
       </c>
       <c r="G19">
-        <v>85.5</v>
+        <v>78.3</v>
       </c>
       <c r="H19">
-        <v>86.7</v>
+        <v>84.5</v>
       </c>
       <c r="I19">
         <v>80</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="K19">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M19">
-        <v>114.5</v>
+        <v>87.3</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>84.5</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>81.3</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4228,7 +4228,7 @@
         <v>40</v>
       </c>
       <c r="D20">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="E20">
         <v>70</v>
@@ -4237,43 +4237,43 @@
         <v>80</v>
       </c>
       <c r="G20">
-        <v>81.8</v>
+        <v>75</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="I20">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L20">
         <v>80</v>
       </c>
       <c r="M20">
-        <v>83.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4287,7 +4287,7 @@
         <v>80</v>
       </c>
       <c r="D21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -4296,43 +4296,43 @@
         <v>95</v>
       </c>
       <c r="G21">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H21">
-        <v>86.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I21">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J21">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="K21">
         <v>100</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4346,7 +4346,7 @@
         <v>95</v>
       </c>
       <c r="D22">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="E22">
         <v>85</v>
@@ -4355,43 +4355,43 @@
         <v>100</v>
       </c>
       <c r="G22">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H22">
-        <v>80</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I22">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J22">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="K22">
         <v>85</v>
       </c>
       <c r="L22">
+        <v>95</v>
+      </c>
+      <c r="M22">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="N22">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="O22">
         <v>90</v>
       </c>
-      <c r="M22">
-        <v>116.4</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
       <c r="P22">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4405,7 +4405,7 @@
         <v>85</v>
       </c>
       <c r="D23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>85</v>
@@ -4414,43 +4414,43 @@
         <v>95</v>
       </c>
       <c r="G23">
-        <v>103.6</v>
+        <v>95</v>
       </c>
       <c r="H23">
-        <v>86.7</v>
+        <v>94.8</v>
       </c>
       <c r="I23">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="K23">
+        <v>82.5</v>
+      </c>
+      <c r="L23">
+        <v>87.5</v>
+      </c>
+      <c r="M23">
+        <v>95.2</v>
+      </c>
+      <c r="N23">
+        <v>94.8</v>
+      </c>
+      <c r="O23">
         <v>80</v>
       </c>
-      <c r="L23">
-        <v>80</v>
-      </c>
-      <c r="M23">
-        <v>114.5</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>78.2</v>
+        <v>71.7</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>101.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="N24">
         <v>0</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4487,7 +4487,7 @@
         <v>85</v>
       </c>
       <c r="D25">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="E25">
         <v>65</v>
@@ -4496,43 +4496,43 @@
         <v>95</v>
       </c>
       <c r="G25">
-        <v>90.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="H25">
-        <v>33.3</v>
+        <v>55.2</v>
       </c>
       <c r="I25">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J25">
+        <v>81.3</v>
+      </c>
+      <c r="K25">
+        <v>57.5</v>
+      </c>
+      <c r="L25">
+        <v>87.5</v>
+      </c>
+      <c r="M25">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="N25">
+        <v>55.2</v>
+      </c>
+      <c r="O25">
         <v>80</v>
       </c>
-      <c r="K25">
-        <v>50</v>
-      </c>
-      <c r="L25">
-        <v>80</v>
-      </c>
-      <c r="M25">
-        <v>101.8</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
       <c r="P25">
-        <v>0</v>
+        <v>81.3</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4546,7 +4546,7 @@
         <v>85</v>
       </c>
       <c r="D26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -4555,43 +4555,43 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H26">
-        <v>80</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I26">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="J26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4605,7 +4605,7 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -4614,43 +4614,43 @@
         <v>100</v>
       </c>
       <c r="G27">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H27">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>100</v>
       </c>
       <c r="J27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4664,7 +4664,7 @@
         <v>50</v>
       </c>
       <c r="D28">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="E28">
         <v>70</v>
@@ -4673,43 +4673,43 @@
         <v>100</v>
       </c>
       <c r="G28">
-        <v>87.3</v>
+        <v>80</v>
       </c>
       <c r="H28">
-        <v>66.7</v>
+        <v>69</v>
       </c>
       <c r="I28">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J28">
-        <v>80</v>
+        <v>62.5</v>
       </c>
       <c r="K28">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L28">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M28">
-        <v>101.8</v>
+        <v>82.5</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4723,7 +4723,7 @@
         <v>85</v>
       </c>
       <c r="D29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>90</v>
@@ -4732,43 +4732,43 @@
         <v>95</v>
       </c>
       <c r="G29">
-        <v>94.5</v>
+        <v>86.7</v>
       </c>
       <c r="H29">
-        <v>66.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I29">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J29">
+        <v>87.5</v>
+      </c>
+      <c r="K29">
+        <v>87.5</v>
+      </c>
+      <c r="L29">
+        <v>85</v>
+      </c>
+      <c r="M29">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="N29">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="O29">
         <v>80</v>
       </c>
-      <c r="K29">
+      <c r="P29">
+        <v>87.5</v>
+      </c>
+      <c r="Q29">
+        <v>87.5</v>
+      </c>
+      <c r="R29">
         <v>85</v>
       </c>
-      <c r="L29">
-        <v>75</v>
-      </c>
-      <c r="M29">
-        <v>116.4</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
       <c r="S29">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4782,7 +4782,7 @@
         <v>90</v>
       </c>
       <c r="D30">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="E30">
         <v>90</v>
@@ -4791,43 +4791,43 @@
         <v>100</v>
       </c>
       <c r="G30">
-        <v>98.2</v>
+        <v>90</v>
       </c>
       <c r="H30">
-        <v>80</v>
+        <v>89.7</v>
       </c>
       <c r="I30">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="J30">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K30">
         <v>90</v>
       </c>
       <c r="L30">
+        <v>95</v>
+      </c>
+      <c r="M30">
+        <v>93.7</v>
+      </c>
+      <c r="N30">
+        <v>89.7</v>
+      </c>
+      <c r="O30">
+        <v>87.5</v>
+      </c>
+      <c r="P30">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="Q30">
         <v>90</v>
       </c>
-      <c r="M30">
-        <v>116.4</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
       <c r="R30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4841,7 +4841,7 @@
         <v>65</v>
       </c>
       <c r="D31">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="E31">
         <v>80</v>
@@ -4850,43 +4850,43 @@
         <v>85</v>
       </c>
       <c r="G31">
-        <v>63.6</v>
+        <v>58.3</v>
       </c>
       <c r="H31">
-        <v>73.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I31">
+        <v>75</v>
+      </c>
+      <c r="J31">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="K31">
         <v>85</v>
       </c>
-      <c r="J31">
-        <v>100</v>
-      </c>
-      <c r="K31">
-        <v>90</v>
-      </c>
       <c r="L31">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="M31">
-        <v>101.8</v>
+        <v>72.2</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4900,7 +4900,7 @@
         <v>95</v>
       </c>
       <c r="D32">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -4909,43 +4909,43 @@
         <v>100</v>
       </c>
       <c r="G32">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H32">
-        <v>93.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I32">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="J32">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -4959,7 +4959,7 @@
         <v>60</v>
       </c>
       <c r="D33">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="E33">
         <v>100</v>
@@ -4968,43 +4968,43 @@
         <v>95</v>
       </c>
       <c r="G33">
-        <v>105.5</v>
+        <v>96.7</v>
       </c>
       <c r="H33">
-        <v>73.3</v>
+        <v>79.3</v>
       </c>
       <c r="I33">
         <v>60</v>
       </c>
       <c r="J33">
-        <v>73.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L33">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="M33">
-        <v>120</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>79.3</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5018,7 +5018,7 @@
         <v>80</v>
       </c>
       <c r="D34">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E34">
         <v>90</v>
@@ -5027,43 +5027,43 @@
         <v>85</v>
       </c>
       <c r="G34">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H34">
-        <v>73.3</v>
+        <v>79.3</v>
       </c>
       <c r="I34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J34">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K34">
         <v>90</v>
       </c>
       <c r="L34">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M34">
-        <v>116.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>79.3</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5077,7 +5077,7 @@
         <v>85</v>
       </c>
       <c r="D35">
-        <v>73.3</v>
+        <v>68.8</v>
       </c>
       <c r="E35">
         <v>100</v>
@@ -5086,43 +5086,43 @@
         <v>90</v>
       </c>
       <c r="G35">
-        <v>92.7</v>
+        <v>85</v>
       </c>
       <c r="H35">
-        <v>93.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I35">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="J35">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="K35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M35">
-        <v>116.4</v>
+        <v>91.3</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>81.3</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5136,7 +5136,7 @@
         <v>65</v>
       </c>
       <c r="D36">
-        <v>60</v>
+        <v>56.3</v>
       </c>
       <c r="E36">
         <v>10</v>
@@ -5145,43 +5145,43 @@
         <v>85</v>
       </c>
       <c r="G36">
-        <v>63.6</v>
+        <v>58.3</v>
       </c>
       <c r="H36">
-        <v>40</v>
+        <v>62.1</v>
       </c>
       <c r="I36">
         <v>65</v>
       </c>
       <c r="J36">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="K36">
-        <v>75</v>
+        <v>42.5</v>
       </c>
       <c r="L36">
         <v>85</v>
       </c>
       <c r="M36">
-        <v>109.1</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>62.1</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2AEV - Estadisticos 20222.xlsx
+++ b/grupos/2AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -197,18 +197,18 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -230,24 +230,30 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
@@ -257,15 +263,21 @@
     <t>BAROJAS</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
     <t>PAUL ARAVIER</t>
   </si>
   <si>
@@ -275,22 +287,31 @@
     <t>DIEGO IVAN</t>
   </si>
   <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>HECTOR ALAN</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
+  </si>
+  <si>
+    <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>ABDIEL NOE</t>
+  </si>
+  <si>
+    <t>OSMAR</t>
+  </si>
+  <si>
     <t>NAHUM HIRAM</t>
   </si>
   <si>
     <t>ERIK</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
   </si>
 </sst>
 </file>
@@ -816,7 +837,7 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -825,16 +846,16 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>6</v>
@@ -869,10 +890,10 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -922,7 +943,7 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -931,13 +952,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>5</v>
@@ -999,7 +1020,7 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1008,16 +1029,16 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -1026,7 +1047,7 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1076,7 +1097,7 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1085,16 +1106,16 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -1109,7 +1130,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1153,7 +1174,7 @@
         <v>4</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1162,13 +1183,13 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1230,7 +1251,7 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1239,13 +1260,13 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>5</v>
@@ -1257,7 +1278,7 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1307,7 +1328,7 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1316,13 +1337,13 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1384,7 +1405,7 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1393,16 +1414,16 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1411,7 +1432,7 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1461,7 +1482,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1470,13 +1491,13 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1488,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1538,7 +1559,7 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1547,13 +1568,13 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1565,13 +1586,13 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1615,7 +1636,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1624,16 +1645,16 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -1642,13 +1663,13 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1692,7 +1713,7 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1701,16 +1722,16 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -1719,7 +1740,7 @@
         <v>5</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1769,7 +1790,7 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -1778,16 +1799,16 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -1802,7 +1823,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1840,19 +1861,19 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -1911,7 +1932,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -1920,16 +1941,16 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -1944,7 +1965,7 @@
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1988,7 +2009,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -1997,13 +2018,13 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2065,7 +2086,7 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2074,16 +2095,16 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -2092,7 +2113,7 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2142,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2151,16 +2172,16 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2219,7 +2240,7 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2228,13 +2249,13 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2252,7 +2273,7 @@
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2272,10 +2293,10 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -2325,7 +2346,7 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2334,13 +2355,13 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
         <v>5</v>
@@ -2402,7 +2423,7 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2411,13 +2432,13 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2435,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2479,7 +2500,7 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2488,13 +2509,13 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2506,13 +2527,13 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2556,7 +2577,7 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2565,16 +2586,16 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -2589,7 +2610,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2633,7 +2654,7 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2642,13 +2663,13 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>5</v>
@@ -2710,7 +2731,7 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -2719,16 +2740,16 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>6</v>
@@ -2737,13 +2758,13 @@
         <v>5</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2787,7 +2808,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -2796,13 +2817,13 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>5</v>
@@ -2864,7 +2885,7 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -2873,16 +2894,16 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -2891,7 +2912,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -2941,7 +2962,7 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -2950,16 +2971,16 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>5</v>
@@ -2968,13 +2989,13 @@
         <v>5</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3018,7 +3039,7 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3027,16 +3048,16 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>5</v>
@@ -3045,13 +3066,13 @@
         <v>5</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3095,7 +3116,7 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3104,13 +3125,13 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>8</v>
@@ -3128,7 +3149,7 @@
         <v>6</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3172,7 +3193,7 @@
         <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3181,13 +3202,13 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T36">
         <v>5</v>
@@ -3359,7 +3380,7 @@
         <v>95.2</v>
       </c>
       <c r="N4">
-        <v>93.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O4">
         <v>90</v>
@@ -3368,13 +3389,13 @@
         <v>84.40000000000001</v>
       </c>
       <c r="Q4">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="R4">
         <v>90</v>
       </c>
       <c r="S4">
-        <v>95.2</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3394,10 +3415,10 @@
         <v>89.7</v>
       </c>
       <c r="N5">
-        <v>86.2</v>
+        <v>89.5</v>
       </c>
       <c r="S5">
-        <v>89.7</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3441,7 +3462,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="N6">
-        <v>86.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="O6">
         <v>82.5</v>
@@ -3450,13 +3471,13 @@
         <v>81.3</v>
       </c>
       <c r="Q6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="R6">
         <v>90</v>
       </c>
       <c r="S6">
-        <v>92.90000000000001</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3559,7 +3580,7 @@
         <v>90.5</v>
       </c>
       <c r="N8">
-        <v>79.3</v>
+        <v>89.5</v>
       </c>
       <c r="O8">
         <v>77.5</v>
@@ -3574,7 +3595,7 @@
         <v>92.5</v>
       </c>
       <c r="S8">
-        <v>90.5</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3618,7 +3639,7 @@
         <v>57.9</v>
       </c>
       <c r="N9">
-        <v>41.4</v>
+        <v>31.6</v>
       </c>
       <c r="O9">
         <v>55</v>
@@ -3627,13 +3648,13 @@
         <v>25</v>
       </c>
       <c r="Q9">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="R9">
         <v>80</v>
       </c>
       <c r="S9">
-        <v>57.9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3677,7 +3698,7 @@
         <v>84.90000000000001</v>
       </c>
       <c r="N10">
-        <v>31</v>
+        <v>23.7</v>
       </c>
       <c r="O10">
         <v>45</v>
@@ -3686,13 +3707,13 @@
         <v>75</v>
       </c>
       <c r="Q10">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="R10">
         <v>87.5</v>
       </c>
       <c r="S10">
-        <v>84.90000000000001</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3751,7 +3772,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3795,7 +3816,7 @@
         <v>88.09999999999999</v>
       </c>
       <c r="N12">
-        <v>86.2</v>
+        <v>94.7</v>
       </c>
       <c r="O12">
         <v>95</v>
@@ -3810,7 +3831,7 @@
         <v>92.5</v>
       </c>
       <c r="S12">
-        <v>88.09999999999999</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3863,7 +3884,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -3913,7 +3934,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N14">
-        <v>89.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O14">
         <v>77.5</v>
@@ -3922,13 +3943,13 @@
         <v>93.8</v>
       </c>
       <c r="Q14">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="R14">
         <v>90</v>
       </c>
       <c r="S14">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3972,7 +3993,7 @@
         <v>96</v>
       </c>
       <c r="N15">
-        <v>93.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="O15">
         <v>90</v>
@@ -3981,13 +4002,13 @@
         <v>81.3</v>
       </c>
       <c r="Q15">
-        <v>82.5</v>
+        <v>78.3</v>
       </c>
       <c r="R15">
         <v>97.5</v>
       </c>
       <c r="S15">
-        <v>96</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4031,7 +4052,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N16">
-        <v>86.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O16">
         <v>77.5</v>
@@ -4046,7 +4067,7 @@
         <v>95</v>
       </c>
       <c r="S16">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4090,7 +4111,7 @@
         <v>87.3</v>
       </c>
       <c r="N17">
-        <v>79.3</v>
+        <v>89.5</v>
       </c>
       <c r="O17">
         <v>60</v>
@@ -4099,13 +4120,13 @@
         <v>93.8</v>
       </c>
       <c r="Q17">
-        <v>72.5</v>
+        <v>78.3</v>
       </c>
       <c r="R17">
         <v>90</v>
       </c>
       <c r="S17">
-        <v>87.3</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4143,19 +4164,19 @@
         <v>69</v>
       </c>
       <c r="N18">
-        <v>63.8</v>
+        <v>48.7</v>
       </c>
       <c r="O18">
         <v>80</v>
       </c>
       <c r="Q18">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="R18">
         <v>82.5</v>
       </c>
       <c r="S18">
-        <v>69</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4199,7 +4220,7 @@
         <v>87.3</v>
       </c>
       <c r="N19">
-        <v>84.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O19">
         <v>80</v>
@@ -4208,13 +4229,13 @@
         <v>81.3</v>
       </c>
       <c r="Q19">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="R19">
         <v>97.5</v>
       </c>
       <c r="S19">
-        <v>87.3</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4258,7 +4279,7 @@
         <v>72.2</v>
       </c>
       <c r="N20">
-        <v>10.3</v>
+        <v>13.2</v>
       </c>
       <c r="O20">
         <v>45</v>
@@ -4267,13 +4288,13 @@
         <v>25</v>
       </c>
       <c r="Q20">
-        <v>35</v>
+        <v>46.7</v>
       </c>
       <c r="R20">
         <v>80</v>
       </c>
       <c r="S20">
-        <v>72.2</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4317,7 +4338,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>93.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O21">
         <v>85</v>
@@ -4326,7 +4347,7 @@
         <v>93.8</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="R21">
         <v>97.5</v>
@@ -4376,7 +4397,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N22">
-        <v>93.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O22">
         <v>90</v>
@@ -4385,13 +4406,13 @@
         <v>87.5</v>
       </c>
       <c r="Q22">
-        <v>85</v>
+        <v>86.7</v>
       </c>
       <c r="R22">
         <v>95</v>
       </c>
       <c r="S22">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4435,7 +4456,7 @@
         <v>95.2</v>
       </c>
       <c r="N23">
-        <v>94.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O23">
         <v>80</v>
@@ -4444,13 +4465,13 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>82.5</v>
+        <v>85</v>
       </c>
       <c r="R23">
         <v>87.5</v>
       </c>
       <c r="S23">
-        <v>95.2</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4473,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="S24">
-        <v>78.59999999999999</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4517,7 +4538,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="N25">
-        <v>55.2</v>
+        <v>60.5</v>
       </c>
       <c r="O25">
         <v>80</v>
@@ -4526,13 +4547,13 @@
         <v>81.3</v>
       </c>
       <c r="Q25">
-        <v>57.5</v>
+        <v>60</v>
       </c>
       <c r="R25">
         <v>87.5</v>
       </c>
       <c r="S25">
-        <v>84.09999999999999</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4576,7 +4597,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>93.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O26">
         <v>82.5</v>
@@ -4694,7 +4715,7 @@
         <v>82.5</v>
       </c>
       <c r="N28">
-        <v>69</v>
+        <v>94.7</v>
       </c>
       <c r="O28">
         <v>55</v>
@@ -4703,13 +4724,13 @@
         <v>62.5</v>
       </c>
       <c r="Q28">
-        <v>75</v>
+        <v>76.7</v>
       </c>
       <c r="R28">
         <v>95</v>
       </c>
       <c r="S28">
-        <v>82.5</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4753,7 +4774,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="N29">
-        <v>75.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="O29">
         <v>80</v>
@@ -4762,13 +4783,13 @@
         <v>87.5</v>
       </c>
       <c r="Q29">
-        <v>87.5</v>
+        <v>58.3</v>
       </c>
       <c r="R29">
         <v>85</v>
       </c>
       <c r="S29">
-        <v>92.09999999999999</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4812,7 +4833,7 @@
         <v>93.7</v>
       </c>
       <c r="N30">
-        <v>89.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O30">
         <v>87.5</v>
@@ -4821,13 +4842,13 @@
         <v>90.59999999999999</v>
       </c>
       <c r="Q30">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="R30">
         <v>95</v>
       </c>
       <c r="S30">
-        <v>93.7</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4871,7 +4892,7 @@
         <v>72.2</v>
       </c>
       <c r="N31">
-        <v>75.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="O31">
         <v>75</v>
@@ -4880,13 +4901,13 @@
         <v>78.09999999999999</v>
       </c>
       <c r="Q31">
-        <v>85</v>
+        <v>78.3</v>
       </c>
       <c r="R31">
         <v>82.5</v>
       </c>
       <c r="S31">
-        <v>72.2</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4930,7 +4951,7 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>96.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O32">
         <v>92.5</v>
@@ -4939,7 +4960,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q32">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -4989,7 +5010,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N33">
-        <v>79.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O33">
         <v>60</v>
@@ -4998,13 +5019,13 @@
         <v>78.09999999999999</v>
       </c>
       <c r="Q33">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="R33">
         <v>87.5</v>
       </c>
       <c r="S33">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5048,7 +5069,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N34">
-        <v>79.3</v>
+        <v>100</v>
       </c>
       <c r="O34">
         <v>90</v>
@@ -5057,13 +5078,13 @@
         <v>84.40000000000001</v>
       </c>
       <c r="Q34">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="R34">
         <v>92.5</v>
       </c>
       <c r="S34">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5107,7 +5128,7 @@
         <v>91.3</v>
       </c>
       <c r="N35">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="O35">
         <v>92.5</v>
@@ -5122,7 +5143,7 @@
         <v>95</v>
       </c>
       <c r="S35">
-        <v>91.3</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5166,7 +5187,7 @@
         <v>75.40000000000001</v>
       </c>
       <c r="N36">
-        <v>62.1</v>
+        <v>73.7</v>
       </c>
       <c r="O36">
         <v>65</v>
@@ -5175,13 +5196,13 @@
         <v>75</v>
       </c>
       <c r="Q36">
-        <v>42.5</v>
+        <v>60</v>
       </c>
       <c r="R36">
         <v>85</v>
       </c>
       <c r="S36">
-        <v>75.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -5302,28 +5323,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2">
-        <v>42.4</v>
+        <v>61.3</v>
       </c>
       <c r="G4" s="2">
-        <v>57.6</v>
+        <v>38.7</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5334,28 +5355,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>42.4</v>
+        <v>61.3</v>
       </c>
       <c r="G5" s="2">
-        <v>57.6</v>
+        <v>38.7</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5366,28 +5387,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" s="2">
-        <v>58.1</v>
+        <v>63.6</v>
       </c>
       <c r="G6" s="2">
-        <v>41.9</v>
+        <v>36.4</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5398,28 +5419,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
       </c>
       <c r="C7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" s="2">
-        <v>61.3</v>
+        <v>66.7</v>
       </c>
       <c r="G7" s="2">
-        <v>38.7</v>
+        <v>33.3</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5469,7 +5490,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5507,16 +5528,16 @@
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5530,16 +5551,16 @@
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5553,10 +5574,10 @@
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5576,10 +5597,10 @@
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5599,16 +5620,16 @@
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5622,16 +5643,16 @@
         <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5639,22 +5660,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920200</v>
+        <v>22330051920371</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5662,22 +5683,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920200</v>
+        <v>22330051920371</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5685,16 +5706,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920202</v>
+        <v>22330051920177</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5708,22 +5729,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920202</v>
+        <v>22330051920187</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5731,22 +5752,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920177</v>
+        <v>22330051920378</v>
       </c>
       <c r="B12" t="s">
         <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5754,22 +5775,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920378</v>
+        <v>22330051920192</v>
       </c>
       <c r="B13" t="s">
         <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5777,7 +5798,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920192</v>
+        <v>22330051920180</v>
       </c>
       <c r="B14" t="s">
         <v>74</v>
@@ -5786,13 +5807,13 @@
         <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5806,10 +5827,10 @@
         <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -5818,6 +5839,52 @@
         <v>57</v>
       </c>
       <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920200</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920202</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2AEV - Estadisticos 20222.xlsx
+++ b/grupos/2AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="101">
   <si>
     <t>Materia</t>
   </si>
@@ -200,15 +200,15 @@
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -230,6 +230,9 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -239,18 +242,15 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -263,6 +263,9 @@
     <t>BAROJAS</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -275,6 +278,9 @@
     <t>PLIEGO</t>
   </si>
   <si>
+    <t>TIZA</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
@@ -287,6 +293,9 @@
     <t>DIEGO IVAN</t>
   </si>
   <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
     <t>ISRAEL</t>
   </si>
   <si>
@@ -299,16 +308,16 @@
     <t>JAIRO YAIR</t>
   </si>
   <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
     <t>ERIK OMAR</t>
   </si>
   <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
     <t>OSMAR</t>
   </si>
   <si>
-    <t>NAHUM HIRAM</t>
+    <t>ALEXANDER</t>
   </si>
   <si>
     <t>ERIK</t>
@@ -840,7 +849,7 @@
         <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -849,7 +858,7 @@
         <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>7</v>
@@ -946,7 +955,7 @@
         <v>3</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -955,7 +964,7 @@
         <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>5</v>
@@ -1023,7 +1032,7 @@
         <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1032,7 +1041,7 @@
         <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>10</v>
@@ -1050,7 +1059,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1100,7 +1109,7 @@
         <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1109,7 +1118,7 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>8</v>
@@ -1118,7 +1127,7 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1177,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1186,7 +1195,7 @@
         <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
         <v>5</v>
@@ -1254,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1263,7 +1272,7 @@
         <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>5</v>
@@ -1281,7 +1290,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1331,7 +1340,7 @@
         <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1340,7 +1349,7 @@
         <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>8</v>
@@ -1358,7 +1367,7 @@
         <v>10</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1408,7 +1417,7 @@
         <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1417,7 +1426,7 @@
         <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>8</v>
@@ -1485,7 +1494,7 @@
         <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1494,7 +1503,7 @@
         <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>10</v>
@@ -1562,7 +1571,7 @@
         <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1571,7 +1580,7 @@
         <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>5</v>
@@ -1639,7 +1648,7 @@
         <v>4</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1648,7 +1657,7 @@
         <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>4</v>
@@ -1657,7 +1666,7 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1666,7 +1675,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -1716,7 +1725,7 @@
         <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1725,7 +1734,7 @@
         <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>5</v>
@@ -1793,7 +1802,7 @@
         <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1802,7 +1811,7 @@
         <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>7</v>
@@ -1820,7 +1829,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -1864,13 +1873,13 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>5</v>
@@ -1935,7 +1944,7 @@
         <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -1944,7 +1953,7 @@
         <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>8</v>
@@ -1953,7 +1962,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -1962,7 +1971,7 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2012,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2021,7 +2030,7 @@
         <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
         <v>5</v>
@@ -2089,7 +2098,7 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2098,7 +2107,7 @@
         <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>10</v>
@@ -2166,7 +2175,7 @@
         <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2175,7 +2184,7 @@
         <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
         <v>6</v>
@@ -2184,7 +2193,7 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2193,7 +2202,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2243,7 +2252,7 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2252,7 +2261,7 @@
         <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>8</v>
@@ -2261,7 +2270,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2270,7 +2279,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2349,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2358,7 +2367,7 @@
         <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
         <v>5</v>
@@ -2426,7 +2435,7 @@
         <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2435,7 +2444,7 @@
         <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>7</v>
@@ -2444,7 +2453,7 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>7</v>
@@ -2503,7 +2512,7 @@
         <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2512,7 +2521,7 @@
         <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>9</v>
@@ -2530,7 +2539,7 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2580,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2589,7 +2598,7 @@
         <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
         <v>8</v>
@@ -2607,7 +2616,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -2657,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2666,7 +2675,7 @@
         <v>5</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
         <v>5</v>
@@ -2734,7 +2743,7 @@
         <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -2743,7 +2752,7 @@
         <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>9</v>
@@ -2811,7 +2820,7 @@
         <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -2820,7 +2829,7 @@
         <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
         <v>5</v>
@@ -2838,7 +2847,7 @@
         <v>5</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -2888,7 +2897,7 @@
         <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -2897,7 +2906,7 @@
         <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>6</v>
@@ -2906,7 +2915,7 @@
         <v>6</v>
       </c>
       <c r="U32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -2965,7 +2974,7 @@
         <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -2974,7 +2983,7 @@
         <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>10</v>
@@ -2992,7 +3001,7 @@
         <v>6</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3042,7 +3051,7 @@
         <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3051,7 +3060,7 @@
         <v>6</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
         <v>8</v>
@@ -3060,7 +3069,7 @@
         <v>6</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -3069,7 +3078,7 @@
         <v>6</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>6</v>
@@ -3119,7 +3128,7 @@
         <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3128,7 +3137,7 @@
         <v>6</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>8</v>
@@ -3137,7 +3146,7 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>5</v>
@@ -3146,7 +3155,7 @@
         <v>7</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -3196,7 +3205,7 @@
         <v>4</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3205,7 +3214,7 @@
         <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
         <v>5</v>
@@ -3223,7 +3232,7 @@
         <v>5</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3383,7 +3392,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="O4">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="P4">
         <v>84.40000000000001</v>
@@ -3392,7 +3401,7 @@
         <v>91.7</v>
       </c>
       <c r="R4">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="S4">
         <v>96.7</v>
@@ -3465,7 +3474,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="O6">
-        <v>82.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="P6">
         <v>81.3</v>
@@ -3474,7 +3483,7 @@
         <v>80</v>
       </c>
       <c r="R6">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="S6">
         <v>92.3</v>
@@ -3524,7 +3533,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="P7">
         <v>96.90000000000001</v>
@@ -3583,7 +3592,7 @@
         <v>89.5</v>
       </c>
       <c r="O8">
-        <v>77.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P8">
         <v>84.40000000000001</v>
@@ -3592,7 +3601,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="S8">
         <v>93.40000000000001</v>
@@ -3642,7 +3651,7 @@
         <v>31.6</v>
       </c>
       <c r="O9">
-        <v>55</v>
+        <v>34.4</v>
       </c>
       <c r="P9">
         <v>25</v>
@@ -3651,7 +3660,7 @@
         <v>16.7</v>
       </c>
       <c r="R9">
-        <v>80</v>
+        <v>51.6</v>
       </c>
       <c r="S9">
         <v>68</v>
@@ -3701,7 +3710,7 @@
         <v>23.7</v>
       </c>
       <c r="O10">
-        <v>45</v>
+        <v>28.1</v>
       </c>
       <c r="P10">
         <v>75</v>
@@ -3710,7 +3719,7 @@
         <v>88.3</v>
       </c>
       <c r="R10">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="S10">
         <v>86.7</v>
@@ -3819,7 +3828,7 @@
         <v>94.7</v>
       </c>
       <c r="O12">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="P12">
         <v>90.59999999999999</v>
@@ -3828,7 +3837,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="S12">
         <v>91.7</v>
@@ -3878,7 +3887,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3937,7 +3946,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="O14">
-        <v>77.5</v>
+        <v>75</v>
       </c>
       <c r="P14">
         <v>93.8</v>
@@ -3946,7 +3955,7 @@
         <v>88.3</v>
       </c>
       <c r="R14">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="S14">
         <v>98.90000000000001</v>
@@ -3996,7 +4005,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="P15">
         <v>81.3</v>
@@ -4005,7 +4014,7 @@
         <v>78.3</v>
       </c>
       <c r="R15">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S15">
         <v>97.2</v>
@@ -4055,7 +4064,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="O16">
-        <v>77.5</v>
+        <v>81.3</v>
       </c>
       <c r="P16">
         <v>84.40000000000001</v>
@@ -4064,7 +4073,7 @@
         <v>90</v>
       </c>
       <c r="R16">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S16">
         <v>98.90000000000001</v>
@@ -4114,7 +4123,7 @@
         <v>89.5</v>
       </c>
       <c r="O17">
-        <v>60</v>
+        <v>59.4</v>
       </c>
       <c r="P17">
         <v>93.8</v>
@@ -4123,7 +4132,7 @@
         <v>78.3</v>
       </c>
       <c r="R17">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="S17">
         <v>91.2</v>
@@ -4167,13 +4176,13 @@
         <v>48.7</v>
       </c>
       <c r="O18">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q18">
         <v>25</v>
       </c>
       <c r="R18">
-        <v>82.5</v>
+        <v>53.2</v>
       </c>
       <c r="S18">
         <v>75.7</v>
@@ -4223,7 +4232,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="O19">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="P19">
         <v>81.3</v>
@@ -4232,7 +4241,7 @@
         <v>90</v>
       </c>
       <c r="R19">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S19">
         <v>91.2</v>
@@ -4282,7 +4291,7 @@
         <v>13.2</v>
       </c>
       <c r="O20">
-        <v>45</v>
+        <v>28.1</v>
       </c>
       <c r="P20">
         <v>25</v>
@@ -4291,7 +4300,7 @@
         <v>46.7</v>
       </c>
       <c r="R20">
-        <v>80</v>
+        <v>51.6</v>
       </c>
       <c r="S20">
         <v>77.90000000000001</v>
@@ -4341,7 +4350,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="O21">
-        <v>85</v>
+        <v>81.3</v>
       </c>
       <c r="P21">
         <v>93.8</v>
@@ -4350,7 +4359,7 @@
         <v>98.3</v>
       </c>
       <c r="R21">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -4400,7 +4409,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="O22">
-        <v>90</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P22">
         <v>87.5</v>
@@ -4409,7 +4418,7 @@
         <v>86.7</v>
       </c>
       <c r="R22">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S22">
         <v>98.90000000000001</v>
@@ -4459,7 +4468,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="O23">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -4468,7 +4477,7 @@
         <v>85</v>
       </c>
       <c r="R23">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="S23">
         <v>96.7</v>
@@ -4541,7 +4550,7 @@
         <v>60.5</v>
       </c>
       <c r="O25">
-        <v>80</v>
+        <v>70.3</v>
       </c>
       <c r="P25">
         <v>81.3</v>
@@ -4550,7 +4559,7 @@
         <v>60</v>
       </c>
       <c r="R25">
-        <v>87.5</v>
+        <v>56.5</v>
       </c>
       <c r="S25">
         <v>86.2</v>
@@ -4600,7 +4609,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="O26">
-        <v>82.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4609,7 +4618,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4718,7 +4727,7 @@
         <v>94.7</v>
       </c>
       <c r="O28">
-        <v>55</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="P28">
         <v>62.5</v>
@@ -4727,7 +4736,7 @@
         <v>76.7</v>
       </c>
       <c r="R28">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S28">
         <v>87.8</v>
@@ -4777,7 +4786,7 @@
         <v>71.09999999999999</v>
       </c>
       <c r="O29">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="P29">
         <v>87.5</v>
@@ -4786,7 +4795,7 @@
         <v>58.3</v>
       </c>
       <c r="R29">
-        <v>85</v>
+        <v>54.8</v>
       </c>
       <c r="S29">
         <v>91.7</v>
@@ -4836,7 +4845,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="O30">
-        <v>87.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P30">
         <v>90.59999999999999</v>
@@ -4845,7 +4854,7 @@
         <v>88.3</v>
       </c>
       <c r="R30">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S30">
         <v>95.59999999999999</v>
@@ -4895,7 +4904,7 @@
         <v>94.7</v>
       </c>
       <c r="O31">
-        <v>75</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="P31">
         <v>78.09999999999999</v>
@@ -4904,7 +4913,7 @@
         <v>78.3</v>
       </c>
       <c r="R31">
-        <v>82.5</v>
+        <v>88.7</v>
       </c>
       <c r="S31">
         <v>77.90000000000001</v>
@@ -4954,7 +4963,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="O32">
-        <v>92.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P32">
         <v>96.90000000000001</v>
@@ -5013,7 +5022,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="O33">
-        <v>60</v>
+        <v>37.5</v>
       </c>
       <c r="P33">
         <v>78.09999999999999</v>
@@ -5022,7 +5031,7 @@
         <v>93.3</v>
       </c>
       <c r="R33">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="S33">
         <v>98.90000000000001</v>
@@ -5072,7 +5081,7 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="P34">
         <v>84.40000000000001</v>
@@ -5081,7 +5090,7 @@
         <v>91.7</v>
       </c>
       <c r="R34">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="S34">
         <v>98.90000000000001</v>
@@ -5131,7 +5140,7 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="P35">
         <v>81.3</v>
@@ -5140,7 +5149,7 @@
         <v>95</v>
       </c>
       <c r="R35">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="S35">
         <v>93.90000000000001</v>
@@ -5190,7 +5199,7 @@
         <v>73.7</v>
       </c>
       <c r="O36">
-        <v>65</v>
+        <v>70.3</v>
       </c>
       <c r="P36">
         <v>75</v>
@@ -5199,7 +5208,7 @@
         <v>60</v>
       </c>
       <c r="R36">
-        <v>85</v>
+        <v>90.3</v>
       </c>
       <c r="S36">
         <v>80.09999999999999</v>
@@ -5300,19 +5309,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2">
-        <v>35.5</v>
+        <v>51.6</v>
       </c>
       <c r="G3" s="2">
-        <v>64.5</v>
+        <v>48.4</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5355,28 +5364,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5">
         <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>61.3</v>
+        <v>63.6</v>
       </c>
       <c r="G5" s="2">
-        <v>38.7</v>
+        <v>36.4</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5387,7 +5396,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -5396,19 +5405,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2">
-        <v>63.6</v>
+        <v>66.7</v>
       </c>
       <c r="G6" s="2">
-        <v>36.4</v>
+        <v>33.3</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5419,28 +5428,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>66.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>33.3</v>
+        <v>19.4</v>
       </c>
       <c r="H7">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5490,7 +5499,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5531,13 +5540,13 @@
         <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5554,13 +5563,13 @@
         <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5577,7 +5586,7 @@
         <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5600,7 +5609,7 @@
         <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5623,13 +5632,13 @@
         <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5646,13 +5655,13 @@
         <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5660,7 +5669,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920371</v>
+        <v>22330051920193</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
@@ -5669,13 +5678,13 @@
         <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5683,7 +5692,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920371</v>
+        <v>22330051920193</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
@@ -5692,13 +5701,13 @@
         <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5706,7 +5715,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920177</v>
+        <v>22330051920371</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
@@ -5715,13 +5724,13 @@
         <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5729,22 +5738,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920187</v>
+        <v>22330051920371</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5752,22 +5761,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920378</v>
+        <v>22330051920177</v>
       </c>
       <c r="B12" t="s">
         <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5775,22 +5784,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920192</v>
+        <v>22330051920187</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5798,16 +5807,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920180</v>
+        <v>22330051920378</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -5821,16 +5830,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920363</v>
+        <v>22330051920359</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -5844,22 +5853,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920200</v>
+        <v>22330051920192</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -5867,16 +5876,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920202</v>
+        <v>22330051920363</v>
       </c>
       <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
         <v>77</v>
       </c>
-      <c r="C17" t="s">
-        <v>85</v>
-      </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -5885,6 +5894,52 @@
         <v>57</v>
       </c>
       <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920201</v>
+      </c>
+      <c r="B18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920202</v>
+      </c>
+      <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2AEV - Estadisticos 20222.xlsx
+++ b/grupos/2AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="96">
   <si>
     <t>Materia</t>
   </si>
@@ -191,24 +191,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -224,10 +224,22 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MORALES</t>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>MOLINA</t>
@@ -236,31 +248,28 @@
     <t>VERA</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>BAROJAS</t>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
   </si>
   <si>
     <t>DE JESUS</t>
@@ -269,58 +278,34 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
     <t>PAUL ARAVIER</t>
   </si>
   <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>FABIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DIEGO IVAN</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
+  </si>
+  <si>
     <t>DAVID</t>
   </si>
   <si>
-    <t>DIEGO IVAN</t>
+    <t>HECTOR ALAN</t>
+  </si>
+  <si>
+    <t>JAIRO YAIR</t>
   </si>
   <si>
     <t>VICTOR MANUEL</t>
   </si>
   <si>
     <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>HECTOR ALAN</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>OSMAR</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ERIK</t>
   </si>
 </sst>
 </file>
@@ -852,7 +837,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>6</v>
@@ -870,7 +855,7 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -958,7 +943,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -1035,7 +1020,7 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>8</v>
@@ -1112,7 +1097,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1189,7 +1174,7 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -1266,7 +1251,7 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1284,7 +1269,7 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1343,7 +1328,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1420,7 +1405,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>9</v>
@@ -1438,7 +1423,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1497,7 +1482,7 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
         <v>6</v>
@@ -1574,7 +1559,7 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>5</v>
@@ -1592,7 +1577,7 @@
         <v>5</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1651,7 +1636,7 @@
         <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>5</v>
@@ -1728,7 +1713,7 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -1746,7 +1731,7 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -1805,7 +1790,7 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -1823,7 +1808,7 @@
         <v>5</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -1947,7 +1932,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>6</v>
@@ -1965,7 +1950,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -2024,7 +2009,7 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>6</v>
@@ -2101,7 +2086,7 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>8</v>
@@ -2119,7 +2104,7 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2178,7 +2163,7 @@
         <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>6</v>
@@ -2196,7 +2181,7 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2255,7 +2240,7 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -2273,7 +2258,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2361,7 +2346,7 @@
         <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>5</v>
@@ -2438,7 +2423,7 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>9</v>
@@ -2456,7 +2441,7 @@
         <v>6</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2515,7 +2500,7 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>6</v>
@@ -2592,7 +2577,7 @@
         <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>5</v>
@@ -2610,7 +2595,7 @@
         <v>5</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -2669,7 +2654,7 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -2746,7 +2731,7 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
         <v>8</v>
@@ -2764,7 +2749,7 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -2823,7 +2808,7 @@
         <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>6</v>
@@ -2841,7 +2826,7 @@
         <v>5</v>
       </c>
       <c r="V31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>5</v>
@@ -2900,7 +2885,7 @@
         <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -2918,7 +2903,7 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -2977,7 +2962,7 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -2995,7 +2980,7 @@
         <v>5</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>6</v>
@@ -3054,7 +3039,7 @@
         <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>6</v>
@@ -3072,7 +3057,7 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>6</v>
@@ -3131,7 +3116,7 @@
         <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>6</v>
@@ -3149,7 +3134,7 @@
         <v>7</v>
       </c>
       <c r="V35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>7</v>
@@ -3208,7 +3193,7 @@
         <v>5</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>8</v>
@@ -3226,7 +3211,7 @@
         <v>5</v>
       </c>
       <c r="V36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3395,7 +3380,7 @@
         <v>87.5</v>
       </c>
       <c r="P4">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Q4">
         <v>91.7</v>
@@ -3477,7 +3462,7 @@
         <v>78.09999999999999</v>
       </c>
       <c r="P6">
-        <v>81.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q6">
         <v>80</v>
@@ -3536,7 +3521,7 @@
         <v>93.8</v>
       </c>
       <c r="P7">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3595,7 +3580,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="P8">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3654,7 +3639,7 @@
         <v>34.4</v>
       </c>
       <c r="P9">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="Q9">
         <v>16.7</v>
@@ -3713,7 +3698,7 @@
         <v>28.1</v>
       </c>
       <c r="P10">
-        <v>75</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Q10">
         <v>88.3</v>
@@ -3831,7 +3816,7 @@
         <v>93.8</v>
       </c>
       <c r="P12">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3949,7 +3934,7 @@
         <v>75</v>
       </c>
       <c r="P14">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Q14">
         <v>88.3</v>
@@ -4008,7 +3993,7 @@
         <v>87.5</v>
       </c>
       <c r="P15">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Q15">
         <v>78.3</v>
@@ -4067,7 +4052,7 @@
         <v>81.3</v>
       </c>
       <c r="P16">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Q16">
         <v>90</v>
@@ -4126,7 +4111,7 @@
         <v>59.4</v>
       </c>
       <c r="P17">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="Q17">
         <v>78.3</v>
@@ -4235,7 +4220,7 @@
         <v>81.3</v>
       </c>
       <c r="P19">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Q19">
         <v>90</v>
@@ -4294,7 +4279,7 @@
         <v>28.1</v>
       </c>
       <c r="P20">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="Q20">
         <v>46.7</v>
@@ -4353,7 +4338,7 @@
         <v>81.3</v>
       </c>
       <c r="P21">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Q21">
         <v>98.3</v>
@@ -4471,7 +4456,7 @@
         <v>81.3</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Q23">
         <v>85</v>
@@ -4553,7 +4538,7 @@
         <v>70.3</v>
       </c>
       <c r="P25">
-        <v>81.3</v>
+        <v>70.8</v>
       </c>
       <c r="Q25">
         <v>60</v>
@@ -4730,7 +4715,7 @@
         <v>65.59999999999999</v>
       </c>
       <c r="P28">
-        <v>62.5</v>
+        <v>81.3</v>
       </c>
       <c r="Q28">
         <v>76.7</v>
@@ -4789,7 +4774,7 @@
         <v>50</v>
       </c>
       <c r="P29">
-        <v>87.5</v>
+        <v>68.8</v>
       </c>
       <c r="Q29">
         <v>58.3</v>
@@ -4848,7 +4833,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="P30">
-        <v>90.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Q30">
         <v>88.3</v>
@@ -4907,7 +4892,7 @@
         <v>71.90000000000001</v>
       </c>
       <c r="P31">
-        <v>78.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Q31">
         <v>78.3</v>
@@ -4966,7 +4951,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="P32">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Q32">
         <v>93.3</v>
@@ -5025,7 +5010,7 @@
         <v>37.5</v>
       </c>
       <c r="P33">
-        <v>78.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Q33">
         <v>93.3</v>
@@ -5084,7 +5069,7 @@
         <v>93.8</v>
       </c>
       <c r="P34">
-        <v>84.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="Q34">
         <v>91.7</v>
@@ -5143,7 +5128,7 @@
         <v>95.3</v>
       </c>
       <c r="P35">
-        <v>81.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Q35">
         <v>95</v>
@@ -5202,7 +5187,7 @@
         <v>70.3</v>
       </c>
       <c r="P36">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="Q36">
         <v>60</v>
@@ -5268,25 +5253,25 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F2" s="2">
-        <v>33.3</v>
+        <v>51.6</v>
       </c>
       <c r="G2" s="2">
-        <v>66.7</v>
+        <v>48.4</v>
       </c>
       <c r="H2">
         <v>5.8</v>
@@ -5300,7 +5285,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -5309,19 +5294,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2">
-        <v>51.6</v>
+        <v>61.3</v>
       </c>
       <c r="G3" s="2">
-        <v>48.4</v>
+        <v>38.7</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5332,28 +5317,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <v>12</v>
       </c>
       <c r="F4" s="2">
-        <v>61.3</v>
+        <v>63.6</v>
       </c>
       <c r="G4" s="2">
-        <v>38.7</v>
+        <v>36.4</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5364,7 +5349,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -5373,19 +5358,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2">
-        <v>63.6</v>
+        <v>66.7</v>
       </c>
       <c r="G5" s="2">
-        <v>36.4</v>
+        <v>33.3</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5396,28 +5381,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>66.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>33.3</v>
+        <v>19.4</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5428,28 +5413,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
       </c>
       <c r="C7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>25</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>80.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="G7" s="2">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5499,7 +5484,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5537,16 +5522,16 @@
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5560,16 +5545,16 @@
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5577,22 +5562,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920188</v>
+        <v>22330051920190</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5600,22 +5585,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920188</v>
+        <v>22330051920190</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5623,22 +5608,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920090</v>
+        <v>22330051920413</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5646,22 +5631,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920090</v>
+        <v>22330051920413</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5669,22 +5654,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920193</v>
+        <v>20330051920090</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5692,19 +5677,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920193</v>
+        <v>20330051920090</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>59</v>
@@ -5715,22 +5700,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920371</v>
+        <v>22330051920356</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5738,22 +5723,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920371</v>
+        <v>22330051920356</v>
       </c>
       <c r="B11" t="s">
         <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5761,19 +5746,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920177</v>
+        <v>22330051920188</v>
       </c>
       <c r="B12" t="s">
         <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>57</v>
@@ -5787,19 +5772,19 @@
         <v>22330051920187</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5813,16 +5798,16 @@
         <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5830,22 +5815,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920359</v>
+        <v>22330051920193</v>
       </c>
       <c r="B15" t="s">
         <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5853,93 +5838,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920192</v>
+        <v>22330051920371</v>
       </c>
       <c r="B16" t="s">
         <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
         <v>57</v>
       </c>
       <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920363</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920201</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920202</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>
